--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
@@ -2650,7 +2650,7 @@
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
         <v>1.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q12" t="n">
         <v>1.47</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
         <v>1.46</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
         <v>1.58</v>
       </c>
       <c r="H16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
         <v>2.04</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="n">
         <v>1.47</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
         <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>2.38</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="I25" t="n">
         <v>4.8</v>
@@ -6732,7 +6732,7 @@
         <v>1.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8988,16 +8988,16 @@
         <v>1.97</v>
       </c>
       <c r="G34" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H34" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FK Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,33 +1859,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hottur</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Hottur</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>1.71</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>1.77</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H12" t="n">
         <v>4.5</v>
       </c>
-      <c r="G12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.63</v>
-      </c>
       <c r="I12" t="n">
-        <v>1.77</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.76</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>1.58</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
         <v>1.46</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,31 +4150,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>1.52</v>
       </c>
       <c r="H17" t="n">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,33 +5161,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
         <v>3.4</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportes Colina</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brujas de Salamanca</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,28 +5674,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Deportes Colina</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Brujas de Salamanca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,33 +6177,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,31 +6690,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
         <v>1.01</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,31 +7960,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lota Schwager</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -8214,28 +8214,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Lota Schwager</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real San Joaquin</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -8468,28 +8468,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Colchagua CD</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Provincial Osorno</t>
+          <t>Real San Joaquin</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Colchagua CD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Provincial Osorno</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
         <v>1.01</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,31 +8976,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -9230,239 +9230,493 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Barra FC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-06-19 04:48:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Inter Limeira</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>2.12</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G36" t="n">
         <v>2.5</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H36" t="n">
         <v>3.75</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>5.2</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>2.76</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>3.85</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>1.39</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q36" t="n">
         <v>2.6</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB35" t="inlineStr">
-        <is>
-          <t>2026-06-19 02:35:44</t>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>2.56</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2626,28 +2626,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.9</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.14</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3134,32 +3134,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.5</v>
       </c>
-      <c r="G11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.54</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.71</v>
       </c>
-      <c r="H12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>1.77</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>1.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,31 +4150,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>2.94</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.78</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="H19" t="n">
-        <v>1.43</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,33 +5415,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="G20" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>3.4</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportes Colina</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brujas de Salamanca</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,28 +5928,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Deportes Colina</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Brujas de Salamanca</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,31 +6944,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7706,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,36 +7955,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.01</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,31 +8214,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lota Schwager</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Lota Schwager</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real San Joaquin</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -8489,7 +8489,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Colchagua CD</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Provincial Osorno</t>
+          <t>Real San Joaquin</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Colchagua CD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Provincial Osorno</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
         <v>1.01</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,31 +9230,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9484,239 +9484,493 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Barra FC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-06-19 07:01:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Inter Limeira</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>2.12</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>2.5</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>3.75</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>5.2</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>2.76</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>3.85</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.39</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q37" t="n">
         <v>2.6</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB36" t="inlineStr">
-        <is>
-          <t>2026-06-19 04:48:46</t>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -869,208 +869,208 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1129,202 +1129,202 @@
         <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
         <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1383,212 +1383,212 @@
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1637,212 +1637,212 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H12" t="n">
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="J12" t="n">
         <v>4.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>1.47</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>2.56</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
         <v>3.55</v>
@@ -1141,7 +1141,7 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -1150,13 +1150,13 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
         <v>1.52</v>
@@ -1177,7 +1177,7 @@
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         <v>40</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1222,55 +1222,55 @@
         <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.19</v>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1646,19 +1646,19 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>1.51</v>
       </c>
       <c r="U7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
         <v>1.48</v>
@@ -2235,52 +2235,52 @@
         <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.5</v>
+        <v>3.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>3.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF7" t="n">
         <v>10</v>
@@ -2289,58 +2289,58 @@
         <v>12</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>38</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
@@ -2408,7 +2408,7 @@
         <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.24</v>
@@ -2417,16 +2417,16 @@
         <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2438,7 +2438,7 @@
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
         <v>36</v>
@@ -2459,7 +2459,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG8" t="n">
         <v>1000</v>
@@ -2504,7 +2504,7 @@
         <v>1.51</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2525,16 +2525,16 @@
         <v>1.51</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BC8" t="n">
         <v>1.51</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
         <v>1.51</v>
@@ -2543,59 +2543,59 @@
         <v>1.51</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>10</v>
       </c>
-      <c r="BU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ8" t="n">
         <v>0</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2671,10 @@
         <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
         <v>1.78</v>
@@ -2692,52 +2692,52 @@
         <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>80</v>
@@ -2746,55 +2746,55 @@
         <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BA9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB9" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>18</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
@@ -2925,7 +2925,7 @@
         <v>1.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
         <v>1.08</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3179,16 +3179,16 @@
         <v>1.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
         <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="V11" t="n">
         <v>2.04</v>
@@ -3200,28 +3200,28 @@
         <v>38</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC11" t="n">
         <v>13.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG11" t="n">
         <v>20</v>
@@ -3230,28 +3230,28 @@
         <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>9.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
         <v>11.5</v>
@@ -3275,7 +3275,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -3287,16 +3287,16 @@
         <v>17.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>15.5</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>2.82</v>
       </c>
       <c r="BN11" t="n">
         <v>11</v>
@@ -3332,13 +3332,13 @@
         <v>36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>15</v>
+        <v>2.68</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>16.5</v>
+        <v>2.7</v>
       </c>
       <c r="BT11" t="n">
         <v>7.6</v>
@@ -3350,23 +3350,23 @@
         <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BX11" t="n">
         <v>29</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>2.64</v>
       </c>
       <c r="BZ11" t="n">
         <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3427,22 +3427,22 @@
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
         <v>2.26</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
@@ -3451,64 +3451,64 @@
         <v>2.72</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
         <v>1.01</v>
@@ -3517,55 +3517,55 @@
         <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
         <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
         <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
         <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK12" t="n">
         <v>6.2</v>
@@ -3574,28 +3574,28 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.9</v>
       </c>
       <c r="BR12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU12" t="n">
         <v>6.6</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="CA12" t="n">
         <v>7.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -3687,13 +3687,13 @@
         <v>1.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="U13" t="n">
         <v>3.1</v>
@@ -3705,176 +3705,176 @@
         <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="n">
         <v>5.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ13" t="n">
         <v>8.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL13" t="n">
         <v>55</v>
       </c>
       <c r="BM13" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP13" t="n">
         <v>18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BR13" t="n">
         <v>22</v>
       </c>
       <c r="BS13" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>6.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV13" t="n">
         <v>16</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BX13" t="n">
         <v>20</v>
       </c>
       <c r="BY13" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>11</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3908,31 +3908,31 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
         <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
         <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
         <v>2.72</v>
@@ -3941,194 +3941,194 @@
         <v>1.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
         <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>1.19</v>
       </c>
       <c r="BN14" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>12.5</v>
+        <v>2.64</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>15.5</v>
+        <v>2.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.5</v>
+        <v>2.36</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>1.71</v>
       </c>
       <c r="I15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="J15" t="n">
         <v>4.7</v>
@@ -4177,16 +4177,16 @@
         <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
         <v>2.78</v>
@@ -4195,112 +4195,112 @@
         <v>1.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
         <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>1.01</v>
@@ -4318,71 +4318,71 @@
         <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW15" t="n">
         <v>6.2</v>
       </c>
-      <c r="BI15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS15" t="n">
+      <c r="BX15" t="n">
         <v>20</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="BY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>18</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4419,10 +4419,10 @@
         <v>1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
         <v>4.9</v>
@@ -4431,34 +4431,34 @@
         <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -4467,64 +4467,64 @@
         <v>2.92</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,110 +4533,110 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
         <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE16" t="n">
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT16" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="R17" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>1.46</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -5029,52 +5029,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G19" t="n">
         <v>2.14</v>
@@ -5190,7 +5190,7 @@
         <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
         <v>1.14</v>
@@ -5217,7 +5217,7 @@
         <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="U19" t="n">
         <v>2.44</v>
@@ -5229,112 +5229,112 @@
         <v>1.87</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH19" t="n">
         <v>6.4</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>21</v>
+        <v>2.88</v>
       </c>
       <c r="BN19" t="n">
         <v>7.6</v>
@@ -5364,13 +5364,13 @@
         <v>19</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8</v>
+        <v>2.56</v>
       </c>
       <c r="BR19" t="n">
         <v>30</v>
       </c>
       <c r="BS19" t="n">
-        <v>12.5</v>
+        <v>2.7</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5382,23 +5382,23 @@
         <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>14</v>
+        <v>2.72</v>
       </c>
       <c r="BX19" t="n">
         <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>16.5</v>
+        <v>2.76</v>
       </c>
       <c r="BZ19" t="n">
         <v>20</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.4</v>
+        <v>2.58</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.4</v>
@@ -5719,7 +5719,7 @@
         <v>1.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
         <v>1.4</v>
@@ -5791,52 +5791,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5937,100 +5937,100 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -6045,122 +6045,122 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O23" t="n">
         <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q23" t="n">
         <v>1.33</v>
@@ -6299,52 +6299,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6553,52 +6553,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,19 +6723,19 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q25" t="n">
         <v>1.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S25" t="n">
         <v>1.15</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
         <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -6983,13 +6983,13 @@
         <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
         <v>2.4</v>
@@ -7010,7 +7010,7 @@
         <v>28</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z26" t="n">
         <v>60</v>
@@ -7019,139 +7019,139 @@
         <v>170</v>
       </c>
       <c r="AB26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
       </c>
       <c r="AN26" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO26" t="n">
         <v>85</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF26" t="n">
         <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BP26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU26" t="n">
         <v>6.2</v>
@@ -7160,13 +7160,13 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G27" t="n">
         <v>2.5</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
         <v>4.8</v>
@@ -7222,16 +7222,16 @@
         <v>2.94</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
@@ -7240,13 +7240,13 @@
         <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -7264,43 +7264,43 @@
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -7318,10 +7318,10 @@
         <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
         <v>1.03</v>
@@ -7330,31 +7330,31 @@
         <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
         <v>1.03</v>
@@ -7390,7 +7390,7 @@
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
@@ -7408,7 +7408,7 @@
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -7461,28 +7461,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
         <v>2.5</v>
@@ -7491,61 +7491,61 @@
         <v>1.55</v>
       </c>
       <c r="P28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X28" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA28" t="n">
         <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE28" t="n">
         <v>65</v>
       </c>
       <c r="AF28" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>95</v>
@@ -7560,76 +7560,76 @@
         <v>80</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.84</v>
+        <v>7.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.92</v>
+        <v>7.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.75</v>
+        <v>36</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.7</v>
+        <v>30</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.65</v>
+        <v>29</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="BJ28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BK28" t="n">
         <v>7.6</v>
@@ -7638,53 +7638,53 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BP28" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BQ28" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS28" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT28" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV28" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BW28" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY28" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA28" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -7727,218 +7727,218 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P29" t="n">
         <v>1.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -7972,13 +7972,13 @@
         <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H30" t="n">
         <v>2.58</v>
       </c>
       <c r="I30" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
@@ -7987,16 +7987,16 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
         <v>2.04</v>
@@ -8005,184 +8005,184 @@
         <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -8226,227 +8226,227 @@
         <v>2.42</v>
       </c>
       <c r="G31" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
         <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K31" t="n">
         <v>3.4</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
         <v>1.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -8495,212 +8495,212 @@
         <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -8749,16 +8749,16 @@
         <v>1000</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
@@ -8767,194 +8767,194 @@
         <v>1.01</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G37" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K37" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -10766,16 +10766,16 @@
         <v>2.56</v>
       </c>
       <c r="G41" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="n">
         <v>3.1</v>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>3.3</v>
@@ -10784,145 +10784,145 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O41" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P41" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R41" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>5.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V41" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB41" t="n">
         <v>9.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF41" t="n">
         <v>19</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.38</v>
+        <v>7.8</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.34</v>
+        <v>6.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.48</v>
+        <v>12</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="G47" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="H47" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J47" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -12320,7 +12320,7 @@
         <v>1.44</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>2.84</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>2.56</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
         <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1144,13 +1144,13 @@
         <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.86</v>
@@ -1159,10 +1159,10 @@
         <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1407,16 +1407,16 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1915,10 +1915,10 @@
         <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
         <v>2.48</v>
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.23</v>
@@ -2160,7 +2160,7 @@
         <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
         <v>1.66</v>
@@ -2235,19 +2235,19 @@
         <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.65</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>3.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -2259,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
@@ -2271,10 +2271,10 @@
         <v>3.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.6</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
@@ -2298,7 +2298,7 @@
         <v>8.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
         <v>16</v>
@@ -2328,7 +2328,7 @@
         <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2420,13 +2420,13 @@
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2438,28 +2438,28 @@
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG8" t="n">
         <v>1000</v>
@@ -2471,16 +2471,16 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
         <v>1000</v>
@@ -2489,58 +2489,58 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
         <v>1.89</v>
@@ -2674,13 +2674,13 @@
         <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
         <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
@@ -2716,7 +2716,7 @@
         <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2728,7 +2728,7 @@
         <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>44</v>
@@ -2737,7 +2737,7 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>80</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2764,37 +2764,37 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
         <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.08</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3305,68 +3305,68 @@
         <v>5.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G12" t="n">
         <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I12" t="n">
         <v>2.58</v>
@@ -3412,7 +3412,7 @@
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>1.18</v>
@@ -3427,22 +3427,22 @@
         <v>1.11</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="U12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.63</v>
@@ -3451,19 +3451,19 @@
         <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y12" t="n">
         <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
@@ -3490,22 +3490,22 @@
         <v>48</v>
       </c>
       <c r="AK12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
         <v>17.5</v>
@@ -3514,13 +3514,13 @@
         <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -3529,7 +3529,7 @@
         <v>16.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
@@ -3541,7 +3541,7 @@
         <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
         <v>18.5</v>
@@ -3550,16 +3550,16 @@
         <v>19</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BF12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BI12" t="n">
         <v>4.5</v>
@@ -3568,7 +3568,7 @@
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL12" t="n">
         <v>55</v>
@@ -3589,7 +3589,7 @@
         <v>6.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS12" t="n">
         <v>6.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
         <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>5.1</v>
@@ -3690,7 +3690,7 @@
         <v>1.69</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
         <v>1.41</v>
@@ -3699,10 +3699,10 @@
         <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
         <v>36</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3941,10 +3941,10 @@
         <v>1.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4067,68 +4067,68 @@
         <v>16</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="I15" t="n">
         <v>1.77</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H16" t="n">
         <v>6.4</v>
@@ -4464,7 +4464,7 @@
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X16" t="n">
         <v>38</v>
@@ -4578,65 +4578,65 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
         <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
         <v>1.47</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4963,10 +4963,10 @@
         <v>1.46</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.49</v>
       </c>
       <c r="G19" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
         <v>5.9</v>
@@ -5187,7 +5187,7 @@
         <v>7.2</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
         <v>5.5</v>
@@ -5211,10 +5211,10 @@
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="T19" t="n">
         <v>1.65</v>
@@ -5226,7 +5226,7 @@
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="X19" t="n">
         <v>32</v>
@@ -5256,16 +5256,16 @@
         <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
         <v>17</v>
@@ -5301,7 +5301,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
@@ -5310,7 +5310,7 @@
         <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
@@ -5325,13 +5325,13 @@
         <v>11</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
@@ -5346,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5358,13 +5358,13 @@
         <v>4.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP19" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
@@ -5376,7 +5376,7 @@
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5394,11 +5394,11 @@
         <v>12.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
         <v>4.8</v>
@@ -5698,7 +5698,7 @@
         <v>2.94</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,13 +5707,13 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
         <v>1.96</v>
@@ -5734,7 +5734,7 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.69</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
         <v>7</v>
@@ -5961,13 +5961,13 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>1.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
         <v>1.63</v>
@@ -5976,7 +5976,7 @@
         <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
         <v>1.73</v>
@@ -6006,7 +6006,7 @@
         <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
         <v>28</v>
@@ -6021,7 +6021,7 @@
         <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>85</v>
@@ -6045,112 +6045,112 @@
         <v>95</v>
       </c>
       <c r="AP22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB22" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="BC22" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="BD22" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="n">
         <v>4.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
         <v>4.5</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT22" t="n">
         <v>10.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.56</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H24" t="n">
         <v>3.2</v>
@@ -6496,7 +6496,7 @@
         <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X24" t="n">
         <v>8.6</v>
@@ -6589,10 +6589,10 @@
         <v>8</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BD24" t="n">
         <v>7.8</v>
@@ -6601,7 +6601,7 @@
         <v>8.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BG24" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>2.68</v>
       </c>
       <c r="G25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I25" t="n">
         <v>3.5</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.65</v>
-      </c>
       <c r="J25" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L25" t="n">
         <v>1.59</v>
@@ -6750,7 +6750,7 @@
         <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
@@ -6807,19 +6807,19 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AR25" t="n">
         <v>4.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AU25" t="n">
         <v>3.15</v>
@@ -6828,7 +6828,7 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AX25" t="n">
         <v>4.2</v>
@@ -6840,28 +6840,28 @@
         <v>4.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BI25" t="n">
         <v>2.2</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7246,13 +7246,13 @@
         <v>1.07</v>
       </c>
       <c r="S27" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.02</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.35</v>
@@ -7748,19 +7748,19 @@
         <v>1.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R29" t="n">
         <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I30" t="n">
         <v>2.82</v>
@@ -8005,7 +8005,7 @@
         <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -8065,7 +8065,7 @@
         <v>38</v>
       </c>
       <c r="AL30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM30" t="n">
         <v>90</v>
@@ -8077,16 +8077,16 @@
         <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
         <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -8095,34 +8095,34 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>14.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF30" t="n">
         <v>16.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8223,37 +8223,37 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G31" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J31" t="n">
         <v>2.88</v>
       </c>
-      <c r="H31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.55</v>
-      </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
         <v>2.38</v>
@@ -8271,10 +8271,10 @@
         <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8385,7 +8385,7 @@
         <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
         <v>1.01</v>
@@ -8394,59 +8394,59 @@
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8755,7 +8755,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O33" t="n">
         <v>1.06</v>
@@ -8764,7 +8764,7 @@
         <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="R33" t="n">
         <v>1.24</v>
@@ -8773,16 +8773,16 @@
         <v>1.05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9018,13 +9018,13 @@
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
         <v>1.12</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="R35" t="n">
         <v>1.24</v>
@@ -9281,10 +9281,10 @@
         <v>1.08</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.1</v>
@@ -9532,13 +9532,13 @@
         <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.07</v>
@@ -9786,13 +9786,13 @@
         <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O38" t="n">
         <v>1.07</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10276,209 +10276,209 @@
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
         <v>2.68</v>
       </c>
       <c r="O39" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P39" t="n">
         <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R39" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V39" t="n">
         <v>1.24</v>
       </c>
       <c r="W39" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS39" t="n">
         <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW39" t="n">
         <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA39" t="n">
         <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
         <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG39" t="n">
         <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BN39" t="n">
         <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10509,230 +10509,230 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10778,19 +10778,19 @@
         <v>2.84</v>
       </c>
       <c r="K41" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P41" t="n">
         <v>1.42</v>
@@ -10799,194 +10799,194 @@
         <v>2.98</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BI41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11029,218 +11029,218 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11283,218 +11283,218 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R43" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11537,218 +11537,218 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11818,13 +11818,13 @@
         <v>1.19</v>
       </c>
       <c r="S45" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T45" t="n">
         <v>2.08</v>
       </c>
       <c r="U45" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="V45" t="n">
         <v>1.41</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12045,22 +12045,22 @@
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K46" t="n">
         <v>1000</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P46" t="n">
         <v>1.24</v>
@@ -12069,194 +12069,194 @@
         <v>1.01</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12299,22 +12299,22 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P47" t="n">
         <v>1.24</v>
@@ -12323,194 +12323,194 @@
         <v>1.01</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12553,218 +12553,218 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
         <v>1.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12813,202 +12813,202 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R49" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G52" t="n">
         <v>2.24</v>
@@ -13590,7 +13590,7 @@
         <v>1.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -899,10 +899,10 @@
         <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.19</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1661,10 +1661,10 @@
         <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>500</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
         <v>1.66</v>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="AT7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -2405,10 +2405,10 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>2.24</v>
@@ -2420,10 +2420,10 @@
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="U8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
@@ -2704,7 +2704,7 @@
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>22</v>
@@ -2716,7 +2716,7 @@
         <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2737,22 +2737,22 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO9" t="n">
         <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2764,10 +2764,10 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
@@ -2776,25 +2776,25 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
         <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>17.5</v>
@@ -3514,7 +3514,7 @@
         <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>21</v>
@@ -3541,7 +3541,7 @@
         <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>18.5</v>
@@ -3556,7 +3556,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="n">
         <v>6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.22</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3941,16 +3941,16 @@
         <v>1.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J15" t="n">
         <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4207,10 +4207,10 @@
         <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
@@ -4249,13 +4249,13 @@
         <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
         <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
         <v>80</v>
@@ -4270,7 +4270,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
         <v>10</v>
@@ -4327,25 +4327,25 @@
         <v>3.8</v>
       </c>
       <c r="BJ15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO15" t="n">
         <v>5.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ15" t="n">
         <v>9.4</v>
@@ -4354,10 +4354,10 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU15" t="n">
         <v>4</v>
@@ -4366,23 +4366,23 @@
         <v>11.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>13</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O17" t="n">
         <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q17" t="n">
         <v>1.47</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.02</v>
@@ -5462,19 +5462,19 @@
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
         <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R23" t="n">
         <v>1.08</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
         <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P24" t="n">
         <v>1.5</v>
@@ -6544,7 +6544,7 @@
         <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN24" t="n">
         <v>50</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
         <v>1.64</v>
       </c>
       <c r="U30" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
         <v>1.54</v>
@@ -8077,7 +8077,7 @@
         <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="AQ30" t="n">
         <v>10.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -8265,10 +8265,10 @@
         <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
         <v>1.33</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8764,7 +8764,7 @@
         <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R33" t="n">
         <v>1.24</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9009,34 +9009,34 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.25</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>1.12</v>
       </c>
       <c r="S34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.02</v>
       </c>
-      <c r="T34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O35" t="n">
         <v>1.08</v>
@@ -9272,7 +9272,7 @@
         <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R35" t="n">
         <v>1.24</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.1</v>
@@ -9532,7 +9532,7 @@
         <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
         <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -9912,55 +9912,55 @@
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
         <v>10.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
         <v>18</v>
@@ -10626,19 +10626,19 @@
         <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT40" t="n">
         <v>7.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV40" t="n">
         <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -10650,25 +10650,25 @@
         <v>16.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BC40" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF40" t="n">
         <v>20</v>
       </c>
       <c r="BG40" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
         <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
         <v>4.9</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
         <v>1.09</v>
@@ -11065,7 +11065,7 @@
         <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
         <v>1.01</v>
@@ -11182,65 +11182,65 @@
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11304,25 +11304,25 @@
         <v>1.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11549,13 +11549,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O44" t="n">
         <v>1.12</v>
       </c>
       <c r="P44" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q44" t="n">
         <v>1.12</v>
@@ -11573,10 +11573,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>2.54</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H45" t="n">
         <v>3.1</v>
@@ -11803,7 +11803,7 @@
         <v>1.12</v>
       </c>
       <c r="N45" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
         <v>1.53</v>
@@ -11812,10 +11812,10 @@
         <v>1.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R45" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S45" t="n">
         <v>5.4</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -12057,13 +12057,13 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O46" t="n">
         <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q46" t="n">
         <v>1.01</v>
@@ -12072,7 +12072,7 @@
         <v>1.16</v>
       </c>
       <c r="S46" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12326,7 +12326,7 @@
         <v>1.16</v>
       </c>
       <c r="S47" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -12562,13 +12562,13 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N48" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P48" t="n">
         <v>1.24</v>
@@ -12580,7 +12580,7 @@
         <v>1.16</v>
       </c>
       <c r="S48" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12816,7 @@
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N49" t="n">
         <v>1.1</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -13061,22 +13061,22 @@
         <v>5.6</v>
       </c>
       <c r="J50" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K50" t="n">
         <v>3.4</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P50" t="n">
         <v>1.43</v>
@@ -13085,194 +13085,194 @@
         <v>2.84</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BI50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -13303,230 +13303,230 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P51" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
@@ -13575,16 +13575,16 @@
         <v>3.5</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P52" t="n">
         <v>1.47</v>
@@ -13593,194 +13593,194 @@
         <v>2.64</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
         <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
         <v>2.32</v>
@@ -2181,7 +2181,7 @@
         <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AR7" t="n">
         <v>20</v>
@@ -2247,7 +2247,7 @@
         <v>32</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>3.8</v>
       </c>
       <c r="BC7" t="n">
         <v>18</v>
@@ -2283,7 +2283,7 @@
         <v>3.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
         <v>12</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2420,10 +2420,10 @@
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
         <v>1.11</v>
@@ -2438,7 +2438,7 @@
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
         <v>36</v>
@@ -2459,7 +2459,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
         <v>1000</v>
@@ -2504,7 +2504,7 @@
         <v>1.51</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2525,16 +2525,16 @@
         <v>1.51</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BC8" t="n">
         <v>1.51</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
         <v>1.51</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2689,10 +2689,10 @@
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
         <v>42</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2764,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
         <v>18.5</v>
@@ -2785,16 +2785,16 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
         <v>1.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
         <v>1.08</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3490,22 +3490,22 @@
         <v>48</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ12" t="n">
         <v>17.5</v>
@@ -3514,13 +3514,13 @@
         <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
         <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
         <v>18.5</v>
@@ -3550,7 +3550,7 @@
         <v>19</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="BF12" t="n">
         <v>8.199999999999999</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3696,10 +3696,10 @@
         <v>1.41</v>
       </c>
       <c r="U13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
         <v>1.42</v>
@@ -3741,13 +3741,13 @@
         <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
         <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>60</v>
@@ -3810,7 +3810,7 @@
         <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O17" t="n">
         <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4954,13 +4954,13 @@
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
         <v>2.26</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5462,7 +5462,7 @@
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6197,13 +6197,13 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6218,19 +6218,19 @@
         <v>1.08</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
         <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.08</v>
       </c>
       <c r="S23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6242,7 +6242,7 @@
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
         <v>1.64</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
         <v>2.98</v>
@@ -6861,7 +6861,7 @@
         <v>2.8</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="BI25" t="n">
         <v>2.2</v>
@@ -6888,41 +6888,41 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6980,19 +6980,19 @@
         <v>1.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7213,13 +7213,13 @@
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7494,13 +7494,13 @@
         <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8504,13 +8504,13 @@
         <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R32" t="n">
         <v>1.16</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8731,118 +8731,118 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="S33" t="n">
-        <v>1.05</v>
+        <v>1.95</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
         <v>1.03</v>
@@ -8851,37 +8851,37 @@
         <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
         <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
         <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
         <v>1.03</v>
@@ -8893,13 +8893,13 @@
         <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI33" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK33" t="n">
         <v>1.01</v>
@@ -8911,25 +8911,25 @@
         <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO33" t="n">
         <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ33" t="n">
         <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS33" t="n">
         <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU33" t="n">
         <v>1.01</v>
@@ -8947,14 +8947,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA33" t="n">
         <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
         <v>1.01</v>
@@ -9024,7 +9024,7 @@
         <v>1.12</v>
       </c>
       <c r="S34" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O36" t="n">
         <v>1.1</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
         <v>3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
         <v>1.11</v>
@@ -10306,7 +10306,7 @@
         <v>1.24</v>
       </c>
       <c r="W39" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X39" t="n">
         <v>11</v>
@@ -10372,7 +10372,7 @@
         <v>22</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT39" t="n">
         <v>6</v>
@@ -10384,7 +10384,7 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX39" t="n">
         <v>9.800000000000001</v>
@@ -10396,7 +10396,7 @@
         <v>20</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB39" t="n">
         <v>17.5</v>
@@ -10405,80 +10405,80 @@
         <v>18</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF39" t="n">
         <v>18.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.46</v>
+        <v>12.5</v>
       </c>
       <c r="BN39" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.46</v>
+        <v>3.6</v>
       </c>
       <c r="BP39" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.46</v>
+        <v>7.4</v>
       </c>
       <c r="BR39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="BT39" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
         <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
@@ -10521,7 +10521,7 @@
         <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K40" t="n">
         <v>3.55</v>
@@ -10557,7 +10557,7 @@
         <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
         <v>1.66</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10877,10 +10877,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT41" t="n">
         <v>4.9</v>
@@ -10892,7 +10892,7 @@
         <v>15.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10904,25 +10904,25 @@
         <v>21</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH41" t="n">
         <v>2.84</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="J43" t="n">
-        <v>1.06</v>
+        <v>3.9</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11295,22 +11295,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="O43" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P43" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="S43" t="n">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="T43" t="n">
         <v>1.11</v>
@@ -11319,10 +11319,10 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11552,10 +11552,10 @@
         <v>1.28</v>
       </c>
       <c r="O44" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P44" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q44" t="n">
         <v>1.12</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="G45" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H45" t="n">
         <v>3.1</v>
       </c>
       <c r="I45" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -11803,19 +11803,19 @@
         <v>1.12</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O45" t="n">
         <v>1.53</v>
       </c>
       <c r="P45" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q45" t="n">
         <v>2.56</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S45" t="n">
         <v>5.4</v>
@@ -11827,7 +11827,7 @@
         <v>1.76</v>
       </c>
       <c r="V45" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
         <v>1.56</v>
@@ -11836,7 +11836,7 @@
         <v>9</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z45" t="n">
         <v>24</v>
@@ -11887,7 +11887,7 @@
         <v>75</v>
       </c>
       <c r="AP45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ45" t="n">
         <v>8.199999999999999</v>
@@ -11896,7 +11896,7 @@
         <v>16</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT45" t="n">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX45" t="n">
         <v>12</v>
@@ -11917,28 +11917,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB45" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BC45" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC45" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD45" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF45" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12057,16 +12057,16 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O46" t="n">
         <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R46" t="n">
         <v>1.16</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R47" t="n">
         <v>1.16</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12562,19 +12562,19 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q48" t="n">
         <v>1.05</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.02</v>
       </c>
       <c r="R48" t="n">
         <v>1.16</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <v>3.4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
         <v>1.14</v>
@@ -13163,10 +13163,10 @@
         <v>8.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT50" t="n">
         <v>4.6</v>
@@ -13178,7 +13178,7 @@
         <v>16.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX50" t="n">
         <v>8</v>
@@ -13190,89 +13190,89 @@
         <v>21</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB50" t="n">
         <v>20</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH50" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="BJ50" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN50" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR50" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT50" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13728,59 +13728,59 @@
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.24</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
         <v>110</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>32</v>
+        <v>3.9</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
         <v>3.35</v>
@@ -2420,7 +2420,7 @@
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
         <v>1.56</v>
@@ -2432,7 +2432,7 @@
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
@@ -2686,7 +2686,7 @@
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X9" t="n">
         <v>15.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.96</v>
@@ -3173,7 +3173,7 @@
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>1.45</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.58</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
         <v>2.32</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.18</v>
@@ -3421,7 +3421,7 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>1.11</v>
@@ -3433,22 +3433,22 @@
         <v>1.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S12" t="n">
         <v>1.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
         <v>50</v>
@@ -3517,10 +3517,10 @@
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BI12" t="n">
         <v>4.5</v>
@@ -3568,13 +3568,13 @@
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL12" t="n">
         <v>55</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN12" t="n">
         <v>7.2</v>
@@ -3610,17 +3610,17 @@
         <v>20</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>11</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
         <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.22</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
@@ -3684,10 +3684,10 @@
         <v>2.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
         <v>2.18</v>
@@ -3696,13 +3696,13 @@
         <v>1.41</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V13" t="n">
         <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X13" t="n">
         <v>36</v>
@@ -3780,7 +3780,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
         <v>1.01</v>
@@ -3822,13 +3822,13 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
@@ -3840,13 +3840,13 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
         <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
@@ -3947,16 +3947,16 @@
         <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
@@ -3995,7 +3995,7 @@
         <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK14" t="n">
         <v>23</v>
@@ -4007,7 +4007,7 @@
         <v>65</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO14" t="n">
         <v>27</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
         <v>5.3</v>
@@ -4168,13 +4168,13 @@
         <v>1.68</v>
       </c>
       <c r="I15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J15" t="n">
         <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4201,13 +4201,13 @@
         <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
         <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W15" t="n">
         <v>1.23</v>
@@ -4258,7 +4258,7 @@
         <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>42</v>
@@ -4330,31 +4330,31 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN15" t="n">
         <v>8.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>32</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>5</v>
@@ -4363,7 +4363,7 @@
         <v>4</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW15" t="n">
         <v>6</v>
@@ -4372,17 +4372,17 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
         <v>13</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -4443,22 +4443,22 @@
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4667,166 +4667,166 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.34</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.41</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4921,46 +4921,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="O18" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.48</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.47</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4969,10 +4969,10 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5193,13 +5193,13 @@
         <v>5.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
@@ -5208,13 +5208,13 @@
         <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
         <v>1.65</v>
@@ -5277,7 +5277,7 @@
         <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AO19" t="n">
         <v>75</v>
@@ -5310,7 +5310,7 @@
         <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
@@ -5325,7 +5325,7 @@
         <v>11</v>
       </c>
       <c r="BD19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5429,220 +5429,220 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>1.56</v>
       </c>
       <c r="G22" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6191,166 +6191,166 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="n">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.08</v>
+        <v>5.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.08</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="S23" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
         <v>1.56</v>
@@ -6487,7 +6487,7 @@
         <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
         <v>1.76</v>
@@ -6499,7 +6499,7 @@
         <v>1.56</v>
       </c>
       <c r="X24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y24" t="n">
         <v>9.800000000000001</v>
@@ -6511,10 +6511,10 @@
         <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
         <v>16.5</v>
@@ -6562,7 +6562,7 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
@@ -6574,7 +6574,7 @@
         <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -6586,7 +6586,7 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB24" t="n">
         <v>36</v>
@@ -6595,16 +6595,16 @@
         <v>32</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
         <v>38</v>
       </c>
       <c r="BG24" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="n">
         <v>2.72</v>
@@ -6616,13 +6616,13 @@
         <v>12</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN24" t="n">
         <v>5.6</v>
@@ -6634,16 +6634,16 @@
         <v>26</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU24" t="n">
         <v>4.9</v>
@@ -6652,23 +6652,23 @@
         <v>34</v>
       </c>
       <c r="BW24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX24" t="n">
         <v>60</v>
       </c>
       <c r="BY24" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ24" t="n">
         <v>60</v>
       </c>
       <c r="CA24" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6953,100 +6953,100 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>2.82</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.45</v>
+        <v>2.48</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -7055,70 +7055,70 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
@@ -7136,7 +7136,7 @@
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
@@ -7243,10 +7243,10 @@
         <v>1.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7461,220 +7461,220 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="J28" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>1.46</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7763,10 +7763,10 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7972,19 +7972,19 @@
         <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H30" t="n">
         <v>2.6</v>
       </c>
       <c r="I30" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.3</v>
@@ -8017,10 +8017,10 @@
         <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X30" t="n">
         <v>20</v>
@@ -8038,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
         <v>15</v>
@@ -8050,7 +8050,7 @@
         <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
@@ -8062,7 +8062,7 @@
         <v>55</v>
       </c>
       <c r="AK30" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="n">
         <v>46</v>
@@ -8077,7 +8077,7 @@
         <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>10.5</v>
@@ -8086,7 +8086,7 @@
         <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -8110,19 +8110,19 @@
         <v>11.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF30" t="n">
         <v>16.5</v>
@@ -8179,7 +8179,7 @@
         <v>6.8</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY30" t="n">
         <v>7.8</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8734,58 +8734,58 @@
         <v>1.38</v>
       </c>
       <c r="G33" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
         <v>5.3</v>
       </c>
       <c r="K33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>1.13</v>
       </c>
       <c r="P33" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U33" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V33" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W33" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="X33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y33" t="n">
         <v>48</v>
@@ -8797,10 +8797,10 @@
         <v>240</v>
       </c>
       <c r="AB33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD33" t="n">
         <v>36</v>
@@ -8809,7 +8809,7 @@
         <v>110</v>
       </c>
       <c r="AF33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG33" t="n">
         <v>13.5</v>
@@ -8818,10 +8818,10 @@
         <v>26</v>
       </c>
       <c r="AI33" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK33" t="n">
         <v>17</v>
@@ -8830,131 +8830,131 @@
         <v>32</v>
       </c>
       <c r="AM33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AO33" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH33" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ33" t="n">
         <v>10.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN33" t="n">
         <v>4.7</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR33" t="n">
         <v>18.5</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT33" t="n">
         <v>12</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
         <v>13.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA40" t="n">
         <v>85</v>
@@ -10626,7 +10626,7 @@
         <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT40" t="n">
         <v>7.6</v>
@@ -10638,7 +10638,7 @@
         <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -10647,7 +10647,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA40" t="n">
         <v>4.4</v>
@@ -10659,10 +10659,10 @@
         <v>4.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF40" t="n">
         <v>20</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         <v>3.15</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
         <v>1.15</v>
@@ -10925,68 +10925,68 @@
         <v>5.1</v>
       </c>
       <c r="BH41" t="n">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11017,230 +11017,230 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="G42" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
-        <v>1.06</v>
+        <v>4.3</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="S42" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="G43" t="n">
         <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I43" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="J43" t="n">
         <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11298,7 +11298,7 @@
         <v>2.58</v>
       </c>
       <c r="O43" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P43" t="n">
         <v>2.58</v>
@@ -11319,7 +11319,7 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="W43" t="n">
         <v>1.14</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>1.46</v>
       </c>
       <c r="J44" t="n">
-        <v>1.06</v>
+        <v>3.25</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.28</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P44" t="n">
-        <v>1.26</v>
+        <v>2.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="S44" t="n">
-        <v>1.12</v>
+        <v>1.94</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11573,10 +11573,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
         <v>1.53</v>
       </c>
       <c r="P45" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q45" t="n">
         <v>2.56</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12565,13 +12565,13 @@
         <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
         <v>1.02</v>
       </c>
       <c r="P48" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q48" t="n">
         <v>1.05</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
         <v>2.62</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="BJ50" t="n">
         <v>13.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13321,13 +13321,13 @@
         <v>3.35</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
         <v>1.12</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O51" t="n">
         <v>1.54</v>
@@ -13465,68 +13465,68 @@
         <v>5.5</v>
       </c>
       <c r="BH51" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ51" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN51" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP51" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT51" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
         <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -941,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
@@ -956,13 +956,13 @@
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
@@ -971,10 +971,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -983,46 +983,46 @@
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1037,50 +1037,50 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW2" t="n">
         <v>30</v>
       </c>
-      <c r="BS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>32</v>
-      </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>38</v>
       </c>
       <c r="BZ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.98</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1141,7 +1141,7 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1368,28 +1368,28 @@
         <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I4" t="n">
         <v>1.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
@@ -1416,7 +1416,7 @@
         <v>2.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
@@ -1530,7 +1530,7 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1542,16 +1542,16 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BQ4" t="n">
         <v>8.4</v>
@@ -1560,22 +1560,22 @@
         <v>55</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>4.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
         <v>13</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="n">
         <v>7.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>1.19</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
         <v>3.6</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.7</v>
@@ -2151,7 +2151,7 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -2160,10 +2160,10 @@
         <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
         <v>3.85</v>
@@ -2172,13 +2172,13 @@
         <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -2187,10 +2187,10 @@
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2226,10 +2226,10 @@
         <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
         <v>26</v>
@@ -2238,13 +2238,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -2256,10 +2256,10 @@
         <v>7.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
@@ -2268,25 +2268,25 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>1.19</v>
       </c>
       <c r="T8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="U8" t="n">
         <v>1.11</v>
@@ -2432,7 +2432,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -2677,10 +2677,10 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V9" t="n">
         <v>1.48</v>
@@ -2761,7 +2761,7 @@
         <v>3.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>4.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -3409,16 +3409,16 @@
         <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.6</v>
@@ -3436,16 +3436,16 @@
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
         <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>2.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
@@ -3702,7 +3702,7 @@
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3816,19 +3816,19 @@
         <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
         <v>5.3</v>
@@ -3840,16 +3840,16 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT13" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7</v>
       </c>
       <c r="BU13" t="n">
         <v>5.3</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.82</v>
@@ -3932,13 +3932,13 @@
         <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
         <v>2.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
         <v>1.64</v>
@@ -3947,16 +3947,16 @@
         <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
         <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X14" t="n">
         <v>32</v>
@@ -3974,7 +3974,7 @@
         <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>16.5</v>
@@ -4013,16 +4013,16 @@
         <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
         <v>14</v>
@@ -4046,10 +4046,10 @@
         <v>10.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
         <v>18</v>
@@ -4058,7 +4058,7 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
         <v>10.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -4413,64 +4413,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="I16" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
         <v>970</v>
@@ -4479,7 +4479,7 @@
         <v>970</v>
       </c>
       <c r="AB16" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -4488,16 +4488,16 @@
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG16" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4521,64 +4521,64 @@
         <v>970</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.76</v>
+        <v>5.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AS16" t="n">
         <v>3.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AX16" t="n">
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -4676,13 +4676,13 @@
         <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
         <v>1.65</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -5178,49 +5178,49 @@
         <v>1.35</v>
       </c>
       <c r="G19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
         <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
         <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>4.8</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>2.78</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
@@ -5229,112 +5229,112 @@
         <v>3.5</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK19" t="n">
         <v>30</v>
       </c>
-      <c r="Z19" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>550</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>480</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>25</v>
-      </c>
       <c r="AL19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="AX19" t="n">
         <v>5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>40</v>
+        <v>2.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
@@ -5465,7 +5465,7 @@
         <v>1.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
         <v>2.16</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="G21" t="n">
         <v>1.63</v>
       </c>
       <c r="H21" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5710,10 +5710,10 @@
         <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>1.56</v>
@@ -5722,13 +5722,13 @@
         <v>1.6</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
         <v>1.16</v>
@@ -5743,10 +5743,10 @@
         <v>34</v>
       </c>
       <c r="Z21" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
         <v>14</v>
@@ -5755,7 +5755,7 @@
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>90</v>
@@ -5770,7 +5770,7 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
         <v>19</v>
@@ -5788,19 +5788,19 @@
         <v>7.6</v>
       </c>
       <c r="AO21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AP21" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5809,13 +5809,13 @@
         <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>17.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
         <v>7.6</v>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -5836,77 +5836,77 @@
         <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF21" t="n">
         <v>5.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH21" t="n">
         <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR21" t="n">
         <v>21</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
         <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
         <v>1.48</v>
@@ -6033,7 +6033,7 @@
         <v>44</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM22" t="n">
         <v>65</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
         <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U23" t="n">
         <v>2.16</v>
@@ -6362,7 +6362,7 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6410,11 +6410,11 @@
         <v>13</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -6448,13 +6448,13 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
         <v>2.18</v>
       </c>
       <c r="I24" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J24" t="n">
         <v>3.8</v>
@@ -6466,10 +6466,10 @@
         <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
@@ -6478,34 +6478,34 @@
         <v>2.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R24" t="n">
         <v>1.69</v>
       </c>
       <c r="S24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V24" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
         <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
         <v>36</v>
@@ -6562,7 +6562,7 @@
         <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT24" t="n">
         <v>14.5</v>
@@ -6574,7 +6574,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX24" t="n">
         <v>19.5</v>
@@ -6589,16 +6589,16 @@
         <v>4</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD24" t="n">
         <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF24" t="n">
         <v>12.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BN25" t="n">
         <v>7.6</v>
@@ -6888,13 +6888,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
@@ -6903,7 +6903,7 @@
         <v>4.7</v>
       </c>
       <c r="BV25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW25" t="n">
         <v>2.72</v>
@@ -6912,17 +6912,17 @@
         <v>44</v>
       </c>
       <c r="BY25" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BZ25" t="n">
         <v>20</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>4.7</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H26" t="n">
         <v>1.66</v>
@@ -7004,7 +7004,7 @@
         <v>2.32</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
         <v>36</v>
@@ -7034,7 +7034,7 @@
         <v>50</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -7049,13 +7049,13 @@
         <v>60</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
         <v>65</v>
       </c>
       <c r="AN26" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
         <v>7.4</v>
@@ -7154,7 +7154,7 @@
         <v>5</v>
       </c>
       <c r="BU26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV26" t="n">
         <v>11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
         <v>1.67</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
         <v>1.14</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -7464,10 +7464,10 @@
         <v>2.56</v>
       </c>
       <c r="G28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H28" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I28" t="n">
         <v>3.25</v>
@@ -7476,22 +7476,22 @@
         <v>2.94</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="n">
         <v>2.26</v>
@@ -7500,10 +7500,10 @@
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
         <v>1.91</v>
@@ -7512,10 +7512,10 @@
         <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
         <v>10.5</v>
@@ -7527,10 +7527,10 @@
         <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
         <v>14.5</v>
@@ -7551,7 +7551,7 @@
         <v>75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK28" t="n">
         <v>38</v>
@@ -7578,7 +7578,7 @@
         <v>14.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
@@ -7590,7 +7590,7 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX28" t="n">
         <v>13.5</v>
@@ -7602,31 +7602,31 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
         <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF28" t="n">
         <v>7</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG28" t="n">
         <v>30</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
@@ -7638,10 +7638,10 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO28" t="n">
         <v>4.7</v>
@@ -7650,41 +7650,41 @@
         <v>24</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR28" t="n">
         <v>44</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT28" t="n">
         <v>6.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV28" t="n">
         <v>28</v>
       </c>
       <c r="BW28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX28" t="n">
         <v>46</v>
       </c>
       <c r="BY28" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
         <v>42</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
         <v>2.84</v>
@@ -7760,7 +7760,7 @@
         <v>1.38</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V29" t="n">
         <v>1.65</v>
@@ -7874,7 +7874,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="n">
         <v>5.9</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G30" t="n">
         <v>1.73</v>
@@ -7981,7 +7981,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
         <v>4.5</v>
@@ -7999,25 +7999,25 @@
         <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
         <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
         <v>1.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
         <v>2.38</v>
@@ -8026,37 +8026,37 @@
         <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA30" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AE30" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
         <v>19</v>
@@ -8068,25 +8068,25 @@
         <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN30" t="n">
         <v>15</v>
       </c>
       <c r="AO30" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AP30" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT30" t="n">
         <v>5.4</v>
@@ -8095,40 +8095,40 @@
         <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY30" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BA30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5</v>
-      </c>
       <c r="BE30" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF30" t="n">
         <v>10</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH30" t="n">
         <v>3.35</v>
@@ -8170,7 +8170,7 @@
         <v>11.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
         <v>2.58</v>
@@ -8232,13 +8232,13 @@
         <v>3.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
         <v>2.88</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
         <v>1.36</v>
@@ -8259,7 +8259,7 @@
         <v>1.89</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
@@ -8271,7 +8271,7 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
         <v>1.63</v>
@@ -8301,19 +8301,19 @@
         <v>55</v>
       </c>
       <c r="AF31" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH31" t="n">
         <v>970</v>
       </c>
       <c r="AI31" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
         <v>34</v>
@@ -8328,7 +8328,7 @@
         <v>970</v>
       </c>
       <c r="AO31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
         <v>1.01</v>
@@ -8343,7 +8343,7 @@
         <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
         <v>5.7</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -8477,31 +8477,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="H32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I32" t="n">
         <v>3.35</v>
       </c>
-      <c r="I32" t="n">
-        <v>3.65</v>
-      </c>
       <c r="J32" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.25</v>
@@ -8516,31 +8516,31 @@
         <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T32" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W32" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="X32" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA32" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB32" t="n">
         <v>12.5</v>
@@ -8552,10 +8552,10 @@
         <v>16.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG32" t="n">
         <v>11.5</v>
@@ -8567,46 +8567,46 @@
         <v>46</v>
       </c>
       <c r="AJ32" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AK32" t="n">
         <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM32" t="n">
         <v>90</v>
       </c>
       <c r="AN32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ32" t="n">
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AT32" t="n">
         <v>9.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX32" t="n">
         <v>11.5</v>
@@ -8621,7 +8621,7 @@
         <v>36</v>
       </c>
       <c r="BB32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC32" t="n">
         <v>17</v>
@@ -8630,67 +8630,67 @@
         <v>25</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG32" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BH32" t="n">
         <v>4.3</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BJ32" t="n">
         <v>10.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO32" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ32" t="n">
         <v>4.3</v>
       </c>
       <c r="BR32" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BX32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY32" t="n">
-        <v>5</v>
       </c>
       <c r="BZ32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
         <v>3.9</v>
       </c>
       <c r="H33" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I33" t="n">
         <v>2.06</v>
@@ -8800,7 +8800,7 @@
         <v>30</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD33" t="n">
         <v>14</v>
@@ -8839,7 +8839,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ33" t="n">
         <v>12.5</v>
@@ -8863,7 +8863,7 @@
         <v>12.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY33" t="n">
         <v>12</v>
@@ -8872,16 +8872,16 @@
         <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BB33" t="n">
         <v>4.1</v>
       </c>
       <c r="BC33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD33" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.9</v>
       </c>
       <c r="BE33" t="n">
         <v>38</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G34" t="n">
         <v>2.76</v>
@@ -9021,10 +9021,10 @@
         <v>2.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
         <v>2.14</v>
@@ -9063,7 +9063,7 @@
         <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG34" t="n">
         <v>13.5</v>
@@ -9096,13 +9096,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT34" t="n">
         <v>6.6</v>
@@ -9126,7 +9126,7 @@
         <v>19.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB34" t="n">
         <v>34</v>
@@ -9135,7 +9135,7 @@
         <v>32</v>
       </c>
       <c r="BD34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE34" t="n">
         <v>10</v>
@@ -9144,7 +9144,7 @@
         <v>38</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH34" t="n">
         <v>2.72</v>
@@ -9174,10 +9174,10 @@
         <v>26</v>
       </c>
       <c r="BQ34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS34" t="n">
         <v>9.199999999999999</v>
@@ -9192,23 +9192,23 @@
         <v>34</v>
       </c>
       <c r="BW34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX34" t="n">
         <v>60</v>
       </c>
       <c r="BY34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ34" t="n">
         <v>60</v>
       </c>
       <c r="CA34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -9239,34 +9239,34 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J35" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N35" t="n">
         <v>2.22</v>
       </c>
       <c r="O35" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P35" t="n">
         <v>1.41</v>
@@ -9287,10 +9287,10 @@
         <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X35" t="n">
         <v>970</v>
@@ -9299,7 +9299,7 @@
         <v>970</v>
       </c>
       <c r="Z35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA35" t="n">
         <v>120</v>
@@ -9314,7 +9314,7 @@
         <v>970</v>
       </c>
       <c r="AE35" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF35" t="n">
         <v>970</v>
@@ -9350,13 +9350,13 @@
         <v>5.7</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT35" t="n">
         <v>5.3</v>
@@ -9365,40 +9365,40 @@
         <v>5.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY35" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BA35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF35" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH35" t="n">
         <v>2.66</v>
@@ -9410,13 +9410,13 @@
         <v>17</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN35" t="n">
         <v>5.2</v>
@@ -9428,16 +9428,16 @@
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU35" t="n">
         <v>5</v>
@@ -9446,7 +9446,7 @@
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -9493,58 +9493,58 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G36" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H36" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O36" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R36" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X36" t="n">
         <v>970</v>
@@ -9553,10 +9553,10 @@
         <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
         <v>970</v>
@@ -9568,7 +9568,7 @@
         <v>970</v>
       </c>
       <c r="AE36" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="n">
         <v>970</v>
@@ -9580,133 +9580,133 @@
         <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ36" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO36" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AP36" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR36" t="n">
         <v>5.1</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT36" t="n">
         <v>6.2</v>
       </c>
       <c r="AU36" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU36" t="n">
         <v>6</v>
       </c>
-      <c r="AV36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BT36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>2.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -9750,16 +9750,16 @@
         <v>6.2</v>
       </c>
       <c r="G37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I37" t="n">
         <v>1.73</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K37" t="n">
         <v>4</v>
@@ -9777,10 +9777,10 @@
         <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R37" t="n">
         <v>1.27</v>
@@ -9789,16 +9789,16 @@
         <v>3.95</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V37" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X37" t="n">
         <v>13.5</v>
@@ -9816,7 +9816,7 @@
         <v>19</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD37" t="n">
         <v>12</v>
@@ -9825,37 +9825,37 @@
         <v>21</v>
       </c>
       <c r="AF37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG37" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="n">
         <v>55</v>
       </c>
       <c r="AJ37" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AK37" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL37" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM37" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN37" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AO37" t="n">
         <v>14</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>6</v>
@@ -9864,10 +9864,10 @@
         <v>7.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU37" t="n">
         <v>7.6</v>
@@ -9876,34 +9876,34 @@
         <v>8.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY37" t="n">
         <v>21</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG37" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
         <v>8.4</v>
       </c>
       <c r="BR37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
         <v>8.6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
         <v>3.35</v>
       </c>
       <c r="K38" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.35</v>
@@ -10031,22 +10031,22 @@
         <v>1.54</v>
       </c>
       <c r="P38" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q38" t="n">
         <v>2.44</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V38" t="n">
         <v>1.09</v>
@@ -10097,7 +10097,7 @@
         <v>24</v>
       </c>
       <c r="AL38" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
@@ -10109,13 +10109,13 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>4.9</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS38" t="n">
         <v>4.3</v>
@@ -10127,7 +10127,7 @@
         <v>7.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW38" t="n">
         <v>4.2</v>
@@ -10148,13 +10148,13 @@
         <v>10</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD38" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF38" t="n">
         <v>8</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -10255,16 +10255,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="H39" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I39" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J39" t="n">
         <v>3.15</v>
@@ -10276,79 +10276,79 @@
         <v>1.57</v>
       </c>
       <c r="M39" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N39" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O39" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P39" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W39" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="X39" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y39" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA39" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AB39" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE39" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG39" t="n">
         <v>12</v>
       </c>
       <c r="AH39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK39" t="n">
         <v>29</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>36</v>
       </c>
       <c r="AL39" t="n">
         <v>70</v>
@@ -10357,52 +10357,52 @@
         <v>300</v>
       </c>
       <c r="AN39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO39" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="AR39" t="n">
         <v>6.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="AW39" t="n">
         <v>7.4</v>
       </c>
       <c r="AX39" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY39" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BA39" t="n">
         <v>7.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC39" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BD39" t="n">
         <v>7</v>
@@ -10411,19 +10411,19 @@
         <v>7.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG39" t="n">
         <v>7.6</v>
       </c>
       <c r="BH39" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK39" t="n">
         <v>8</v>
@@ -10432,16 +10432,16 @@
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ39" t="n">
         <v>9.6</v>
@@ -10450,25 +10450,25 @@
         <v>44</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV39" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BW39" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>2.46</v>
       </c>
       <c r="G40" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="H40" t="n">
         <v>2.18</v>
       </c>
       <c r="I40" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
         <v>7.4</v>
@@ -10533,22 +10533,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.12</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R40" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G41" t="n">
         <v>1.38</v>
@@ -10772,46 +10772,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N41" t="n">
         <v>5.5</v>
       </c>
-      <c r="K41" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O41" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R41" t="n">
         <v>1.62</v>
       </c>
       <c r="S41" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T41" t="n">
         <v>1.93</v>
       </c>
       <c r="U41" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W41" t="n">
         <v>3.6</v>
@@ -10823,7 +10823,7 @@
         <v>48</v>
       </c>
       <c r="Z41" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
@@ -10883,7 +10883,7 @@
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU41" t="n">
         <v>10</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>3.7</v>
       </c>
       <c r="G43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H43" t="n">
         <v>1.71</v>
@@ -11283,7 +11283,7 @@
         <v>2.06</v>
       </c>
       <c r="J43" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
         <v>4.8</v>
@@ -11295,7 +11295,7 @@
         <v>1.04</v>
       </c>
       <c r="N43" t="n">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="O43" t="n">
         <v>1.2</v>
@@ -11304,7 +11304,7 @@
         <v>2.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R43" t="n">
         <v>1.46</v>
@@ -11316,7 +11316,7 @@
         <v>1.6</v>
       </c>
       <c r="U43" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V43" t="n">
         <v>1.94</v>
@@ -11328,37 +11328,37 @@
         <v>25</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA43" t="n">
         <v>24</v>
       </c>
       <c r="AB43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD43" t="n">
         <v>12</v>
       </c>
       <c r="AE43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH43" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ43" t="n">
         <v>110</v>
@@ -11376,125 +11376,125 @@
         <v>50</v>
       </c>
       <c r="AO43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AR43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU43" t="n">
         <v>3.7</v>
       </c>
-      <c r="AS43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AV43" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW43" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AX43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY43" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY43" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ43" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG43" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BH43" t="n">
         <v>4.4</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ43" t="n">
         <v>10.5</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN43" t="n">
         <v>9</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP43" t="n">
         <v>38</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR43" t="n">
         <v>42</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT43" t="n">
         <v>5.2</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BV43" t="n">
         <v>13.5</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX43" t="n">
         <v>25</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ43" t="n">
         <v>18.5</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11591,7 @@
         <v>40</v>
       </c>
       <c r="AB44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC44" t="n">
         <v>10.5</v>
@@ -11624,13 +11624,13 @@
         <v>42</v>
       </c>
       <c r="AM44" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN44" t="n">
         <v>25</v>
       </c>
       <c r="AO44" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP44" t="n">
         <v>17</v>
@@ -11648,7 +11648,7 @@
         <v>11.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV44" t="n">
         <v>10.5</v>
@@ -11666,22 +11666,22 @@
         <v>12</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC44" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC44" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF44" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG44" t="n">
         <v>12</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
         <v>2.6</v>
       </c>
       <c r="I45" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J45" t="n">
         <v>3.4</v>
@@ -11818,7 +11818,7 @@
         <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
         <v>1.66</v>
@@ -11827,16 +11827,16 @@
         <v>2.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W45" t="n">
         <v>1.51</v>
       </c>
       <c r="X45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z45" t="n">
         <v>23</v>
@@ -11896,7 +11896,7 @@
         <v>13.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT45" t="n">
         <v>11</v>
@@ -11923,16 +11923,16 @@
         <v>30</v>
       </c>
       <c r="BB45" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC45" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD45" t="n">
         <v>27</v>
       </c>
       <c r="BE45" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF45" t="n">
         <v>16.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -12287,178 +12287,178 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="G47" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="I47" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="K47" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="L47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M47" t="n">
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R47" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="S47" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="T47" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="U47" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="V47" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W47" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="X47" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Y47" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD47" t="n">
         <v>46</v>
       </c>
-      <c r="Z47" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB47" t="n">
+      <c r="AE47" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG47" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC47" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE47" t="n">
+      <c r="AH47" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI47" t="n">
         <v>110</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AJ47" t="n">
         <v>14</v>
       </c>
-      <c r="AG47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AK47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL47" t="n">
         <v>32</v>
       </c>
       <c r="AM47" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN47" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AO47" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AP47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI47" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI47" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BJ47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
@@ -12467,16 +12467,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN47" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO47" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BP47" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BQ47" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR47" t="n">
         <v>19</v>
@@ -12485,32 +12485,32 @@
         <v>6.4</v>
       </c>
       <c r="BT47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ47" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA47" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
         <v>2.64</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H48" t="n">
         <v>2.78</v>
@@ -12652,55 +12652,55 @@
         <v>7.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH48" t="n">
         <v>3</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -12795,100 +12795,100 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H49" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="I49" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O49" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R49" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S49" t="n">
-        <v>1.59</v>
+        <v>3.45</v>
       </c>
       <c r="T49" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U49" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W49" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI49" t="n">
         <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL49" t="n">
         <v>1000</v>
@@ -12897,64 +12897,64 @@
         <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO49" t="n">
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G50" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H50" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I50" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
-        <v>1.06</v>
+        <v>2.88</v>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -13073,22 +13073,22 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O50" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="P50" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="R50" t="n">
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.57</v>
+        <v>2.74</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -13097,10 +13097,10 @@
         <v>1.11</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>1.02</v>
+        <v>1.91</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -13303,166 +13303,166 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G51" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H51" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I51" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J51" t="n">
-        <v>1.06</v>
+        <v>2.88</v>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N51" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P51" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="R51" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S51" t="n">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="T51" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W51" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM51" t="n">
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,22 +13581,22 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
         <v>1.07</v>
       </c>
       <c r="P52" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q52" t="n">
         <v>1.07</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="S52" t="n">
-        <v>1.07</v>
+        <v>1.72</v>
       </c>
       <c r="T52" t="n">
         <v>1.11</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13841,19 +13841,19 @@
         <v>1.07</v>
       </c>
       <c r="P53" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R53" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S53" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T53" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U53" t="n">
         <v>1.11</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,34 +14089,34 @@
         <v>1.02</v>
       </c>
       <c r="N54" t="n">
-        <v>1.26</v>
+        <v>2.92</v>
       </c>
       <c r="O54" t="n">
         <v>1.1</v>
       </c>
       <c r="P54" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q54" t="n">
         <v>1.1</v>
       </c>
       <c r="R54" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="S54" t="n">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="T54" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U54" t="n">
         <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -14319,230 +14319,230 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M55" t="n">
         <v>1.02</v>
       </c>
       <c r="N55" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="O55" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P55" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="R55" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="S55" t="n">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="T55" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="U55" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y55" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z55" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB55" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG55" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM55" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG55" t="n">
         <v>1.01</v>
       </c>
       <c r="BH55" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BN55" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP55" t="n">
         <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT55" t="n">
         <v>1000</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -14576,55 +14576,55 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H56" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
         <v>3.1</v>
       </c>
       <c r="K56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M56" t="n">
         <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O56" t="n">
         <v>1.49</v>
       </c>
       <c r="P56" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R56" t="n">
         <v>1.21</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T56" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U56" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V56" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W56" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X56" t="n">
         <v>11</v>
@@ -14633,22 +14633,22 @@
         <v>14.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA56" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB56" t="n">
         <v>7.2</v>
       </c>
       <c r="AC56" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE56" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF56" t="n">
         <v>12</v>
@@ -14657,10 +14657,10 @@
         <v>13</v>
       </c>
       <c r="AH56" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI56" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ56" t="n">
         <v>32</v>
@@ -14672,73 +14672,73 @@
         <v>65</v>
       </c>
       <c r="AM56" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO56" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP56" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR56" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT56" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU56" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE56" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV56" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ56" t="n">
+      <c r="BF56" t="n">
         <v>18</v>
       </c>
-      <c r="BA56" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG56" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH56" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ56" t="n">
         <v>11.5</v>
@@ -14753,7 +14753,7 @@
         <v>12.5</v>
       </c>
       <c r="BN56" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO56" t="n">
         <v>3.65</v>
@@ -14771,7 +14771,7 @@
         <v>10</v>
       </c>
       <c r="BT56" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU56" t="n">
         <v>6</v>
@@ -14780,7 +14780,7 @@
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -14830,22 +14830,22 @@
         <v>2.32</v>
       </c>
       <c r="G57" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H57" t="n">
         <v>3.2</v>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J57" t="n">
         <v>3.3</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L57" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="n">
         <v>1.09</v>
@@ -14857,7 +14857,7 @@
         <v>1.42</v>
       </c>
       <c r="P57" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
         <v>2.2</v>
@@ -14872,7 +14872,7 @@
         <v>1.92</v>
       </c>
       <c r="U57" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V57" t="n">
         <v>1.39</v>
@@ -14905,7 +14905,7 @@
         <v>55</v>
       </c>
       <c r="AF57" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG57" t="n">
         <v>14</v>
@@ -14917,7 +14917,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK57" t="n">
         <v>36</v>
@@ -14935,7 +14935,7 @@
         <v>65</v>
       </c>
       <c r="AP57" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ57" t="n">
         <v>8.199999999999999</v>
@@ -14944,7 +14944,7 @@
         <v>16.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT57" t="n">
         <v>6.4</v>
@@ -14956,7 +14956,7 @@
         <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX57" t="n">
         <v>10.5</v>
@@ -14968,16 +14968,16 @@
         <v>17.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB57" t="n">
         <v>4.3</v>
       </c>
       <c r="BC57" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE57" t="n">
         <v>4.7</v>
@@ -14992,7 +14992,7 @@
         <v>3.05</v>
       </c>
       <c r="BI57" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ57" t="n">
         <v>10.5</v>
@@ -15004,7 +15004,7 @@
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN57" t="n">
         <v>5.2</v>
@@ -15016,41 +15016,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR57" t="n">
         <v>38</v>
       </c>
       <c r="BS57" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT57" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV57" t="n">
         <v>30</v>
       </c>
       <c r="BW57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA57" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY57" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA57" t="n">
-        <v>11</v>
-      </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -15081,16 +15081,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G58" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H58" t="n">
         <v>5.1</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -15099,19 +15099,19 @@
         <v>3.4</v>
       </c>
       <c r="L58" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M58" t="n">
         <v>1.14</v>
       </c>
       <c r="N58" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>1.6</v>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q58" t="n">
         <v>2.8</v>
@@ -15129,13 +15129,13 @@
         <v>1.62</v>
       </c>
       <c r="V58" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W58" t="n">
         <v>1.96</v>
       </c>
       <c r="X58" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y58" t="n">
         <v>14.5</v>
@@ -15147,7 +15147,7 @@
         <v>220</v>
       </c>
       <c r="AB58" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC58" t="n">
         <v>8.4</v>
@@ -15192,55 +15192,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ58" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR58" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD58" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS58" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU58" t="n">
+      <c r="BE58" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF58" t="n">
         <v>20</v>
       </c>
       <c r="BG58" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH58" t="n">
         <v>2.64</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -15440,22 +15440,22 @@
         <v>46</v>
       </c>
       <c r="AO59" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AP59" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR59" t="n">
         <v>10</v>
       </c>
       <c r="AS59" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT59" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AU59" t="n">
         <v>9</v>
@@ -15464,34 +15464,34 @@
         <v>8</v>
       </c>
       <c r="AW59" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AX59" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AY59" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA59" t="n">
         <v>17.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG59" t="n">
         <v>4.3</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G60" t="n">
         <v>1.71</v>
@@ -15598,7 +15598,7 @@
         <v>4.7</v>
       </c>
       <c r="I60" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J60" t="n">
         <v>4.6</v>
@@ -15616,16 +15616,16 @@
         <v>7.2</v>
       </c>
       <c r="O60" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P60" t="n">
         <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R60" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S60" t="n">
         <v>1.93</v>
@@ -15685,7 +15685,7 @@
         <v>970</v>
       </c>
       <c r="AL60" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM60" t="n">
         <v>60</v>
@@ -15697,19 +15697,19 @@
         <v>32</v>
       </c>
       <c r="AP60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ60" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ60" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AR60" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT60" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU60" t="n">
         <v>10</v>
@@ -15718,7 +15718,7 @@
         <v>16</v>
       </c>
       <c r="AW60" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX60" t="n">
         <v>11.5</v>
@@ -15730,10 +15730,10 @@
         <v>12.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB60" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC60" t="n">
         <v>11.5</v>
@@ -15742,7 +15742,7 @@
         <v>5.9</v>
       </c>
       <c r="BE60" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF60" t="n">
         <v>4.1</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
         <v>1.44</v>
       </c>
       <c r="I61" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J61" t="n">
         <v>5</v>
@@ -15936,7 +15936,7 @@
         <v>180</v>
       </c>
       <c r="AK61" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL61" t="n">
         <v>70</v>
@@ -15966,7 +15966,7 @@
         <v>5.5</v>
       </c>
       <c r="AU61" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AV61" t="n">
         <v>8.4</v>
@@ -15993,7 +15993,7 @@
         <v>5.8</v>
       </c>
       <c r="BD61" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE61" t="n">
         <v>5.8</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -16100,13 +16100,13 @@
         <v>2.7</v>
       </c>
       <c r="G62" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H62" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J62" t="n">
         <v>3</v>
@@ -16124,7 +16124,7 @@
         <v>2.66</v>
       </c>
       <c r="O62" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P62" t="n">
         <v>1.55</v>
@@ -16148,10 +16148,10 @@
         <v>1.44</v>
       </c>
       <c r="W62" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X62" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y62" t="n">
         <v>9.4</v>
@@ -16187,10 +16187,10 @@
         <v>85</v>
       </c>
       <c r="AJ62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK62" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL62" t="n">
         <v>75</v>
@@ -16199,10 +16199,10 @@
         <v>200</v>
       </c>
       <c r="AN62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO62" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP62" t="n">
         <v>7.8</v>
@@ -16214,7 +16214,7 @@
         <v>17</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT62" t="n">
         <v>6.4</v>
@@ -16226,7 +16226,7 @@
         <v>11</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX62" t="n">
         <v>12.5</v>
@@ -16235,92 +16235,92 @@
         <v>10</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB62" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC62" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF62" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE62" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG62" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
       </c>
       <c r="BI62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ62" t="n">
         <v>1000</v>
       </c>
       <c r="BK62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN62" t="n">
         <v>1000</v>
       </c>
       <c r="BO62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP62" t="n">
         <v>1000</v>
       </c>
       <c r="BQ62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT62" t="n">
         <v>1000</v>
       </c>
       <c r="BU62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
         <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K63" t="n">
         <v>1000</v>
@@ -16375,19 +16375,19 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O63" t="n">
         <v>1.01</v>
       </c>
       <c r="P63" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q63" t="n">
         <v>1.02</v>
       </c>
       <c r="R63" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S63" t="n">
         <v>1.48</v>
@@ -16399,7 +16399,7 @@
         <v>1.11</v>
       </c>
       <c r="V63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
         <v>1.02</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -16883,13 +16883,13 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O65" t="n">
         <v>1.02</v>
       </c>
       <c r="P65" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q65" t="n">
         <v>1.05</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -17370,19 +17370,19 @@
         <v>1.86</v>
       </c>
       <c r="G67" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H67" t="n">
         <v>4.9</v>
       </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
         <v>2.96</v>
       </c>
       <c r="K67" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L67" t="n">
         <v>1.51</v>
@@ -17412,7 +17412,7 @@
         <v>2.26</v>
       </c>
       <c r="U67" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V67" t="n">
         <v>1.2</v>
@@ -17436,7 +17436,7 @@
         <v>7.2</v>
       </c>
       <c r="AC67" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD67" t="n">
         <v>28</v>
@@ -17484,49 +17484,49 @@
         <v>4.2</v>
       </c>
       <c r="AS67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT67" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>4.7</v>
       </c>
       <c r="AU67" t="n">
         <v>5.8</v>
       </c>
       <c r="AV67" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW67" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX67" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY67" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA67" t="n">
         <v>4.5</v>
       </c>
       <c r="BB67" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC67" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BD67" t="n">
         <v>4.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF67" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG67" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH67" t="n">
         <v>2.7</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -17621,13 +17621,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G68" t="n">
         <v>2.32</v>
       </c>
       <c r="H68" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I68" t="n">
         <v>4.3</v>
@@ -17648,19 +17648,19 @@
         <v>2.68</v>
       </c>
       <c r="O68" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P68" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R68" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S68" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T68" t="n">
         <v>2.12</v>
@@ -17669,13 +17669,13 @@
         <v>1.79</v>
       </c>
       <c r="V68" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W68" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X68" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y68" t="n">
         <v>12.5</v>
@@ -17696,7 +17696,7 @@
         <v>18</v>
       </c>
       <c r="AE68" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF68" t="n">
         <v>14.5</v>
@@ -17705,13 +17705,13 @@
         <v>13.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI68" t="n">
         <v>100</v>
       </c>
       <c r="AJ68" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK68" t="n">
         <v>36</v>
@@ -17720,7 +17720,7 @@
         <v>65</v>
       </c>
       <c r="AM68" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN68" t="n">
         <v>36</v>
@@ -17738,7 +17738,7 @@
         <v>20</v>
       </c>
       <c r="AS68" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT68" t="n">
         <v>6</v>
@@ -17750,7 +17750,7 @@
         <v>14.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX68" t="n">
         <v>10</v>
@@ -17765,22 +17765,22 @@
         <v>6.2</v>
       </c>
       <c r="BB68" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC68" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD68" t="n">
         <v>6</v>
       </c>
       <c r="BE68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG68" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG68" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH68" t="n">
         <v>2.84</v>
@@ -17789,7 +17789,7 @@
         <v>2.32</v>
       </c>
       <c r="BJ68" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK68" t="n">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN68" t="n">
         <v>5</v>
@@ -17810,13 +17810,13 @@
         <v>20</v>
       </c>
       <c r="BQ68" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR68" t="n">
         <v>46</v>
       </c>
       <c r="BS68" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT68" t="n">
         <v>7.4</v>
@@ -17828,23 +17828,23 @@
         <v>1000</v>
       </c>
       <c r="BW68" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX68" t="n">
         <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ68" t="n">
         <v>1000</v>
       </c>
       <c r="CA68" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G69" t="n">
         <v>2.26</v>
@@ -17890,7 +17890,7 @@
         <v>2.92</v>
       </c>
       <c r="K69" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -857,67 +857,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.35</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
@@ -926,55 +926,55 @@
         <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK2" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -983,104 +983,104 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10</v>
       </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1141,7 +1141,7 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -1150,13 +1150,13 @@
         <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
         <v>1.51</v>
@@ -1186,7 +1186,7 @@
         <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
         <v>22</v>
@@ -1195,28 +1195,28 @@
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>17.5</v>
@@ -1228,49 +1228,49 @@
         <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
         <v>21</v>
       </c>
       <c r="BD3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.1</v>
@@ -1282,13 +1282,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>5.9</v>
@@ -1300,13 +1300,13 @@
         <v>18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>27</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
@@ -1318,23 +1318,23 @@
         <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>19</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1389,40 +1389,40 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W4" t="n">
         <v>1.21</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
         <v>11.5</v>
@@ -1434,49 +1434,49 @@
         <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AL4" t="n">
         <v>320</v>
       </c>
       <c r="AM4" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
         <v>8.6</v>
@@ -1485,43 +1485,43 @@
         <v>15</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
         <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AY4" t="n">
         <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
         <v>9.4</v>
@@ -1530,37 +1530,37 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
         <v>46</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
         <v>55</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>4.6</v>
@@ -1569,16 +1569,16 @@
         <v>3.55</v>
       </c>
       <c r="BV4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
         <v>2.5</v>
@@ -1634,10 +1634,10 @@
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
@@ -1652,7 +1652,7 @@
         <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.9</v>
@@ -1673,10 +1673,10 @@
         <v>1.59</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,7 +1685,7 @@
         <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
         <v>500</v>
@@ -1739,10 +1739,10 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>7</v>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
         <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
@@ -1912,22 +1912,22 @@
         <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
         <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1939,7 +1939,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
         <v>42</v>
@@ -1975,7 +1975,7 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
@@ -1987,7 +1987,7 @@
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS6" t="n">
         <v>4.4</v>
@@ -2017,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="BC6" t="n">
         <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BE6" t="n">
         <v>2.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2145,46 +2145,46 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W7" t="n">
         <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>16</v>
@@ -2199,7 +2199,7 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>65</v>
@@ -2229,7 +2229,7 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -2241,10 +2241,10 @@
         <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -2253,7 +2253,7 @@
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
         <v>9.6</v>
@@ -2265,13 +2265,13 @@
         <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>34</v>
@@ -2280,67 +2280,67 @@
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.76</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.78</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
         <v>22</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.68</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.76</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.67</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>950</v>
       </c>
-      <c r="AC8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.52</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.44</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.47</v>
+        <v>6.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.42</v>
+        <v>5.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.48</v>
+        <v>5.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.52</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.51</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.58</v>
+        <v>3.35</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2635,55 +2635,55 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.53</v>
@@ -2695,7 +2695,7 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
@@ -2737,10 +2737,10 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
         <v>7.6</v>
@@ -2752,19 +2752,19 @@
         <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2773,92 +2773,92 @@
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BE9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.7</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,13 +2955,13 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AC10" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>170</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2970,10 +2970,10 @@
         <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2988,131 +2988,131 @@
         <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.16</v>
+        <v>5.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.18</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.16</v>
+        <v>5.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.15</v>
+        <v>4.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.16</v>
+        <v>5.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.18</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.16</v>
+        <v>4.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.17</v>
+        <v>5.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.18</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.18</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>5.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -3170,7 +3170,7 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
@@ -3200,7 +3200,7 @@
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3212,10 +3212,10 @@
         <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
@@ -3266,7 +3266,7 @@
         <v>1.71</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.56</v>
+        <v>5.6</v>
       </c>
       <c r="AV11" t="n">
         <v>1.59</v>
@@ -3305,68 +3305,68 @@
         <v>2.18</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -3409,10 +3409,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -3508,7 +3508,7 @@
         <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
@@ -3517,16 +3517,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
         <v>18.5</v>
@@ -3547,16 +3547,16 @@
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -3681,25 +3681,25 @@
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.83</v>
@@ -3720,7 +3720,7 @@
         <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
         <v>23</v>
@@ -3747,7 +3747,7 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
@@ -3762,13 +3762,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3780,7 +3780,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3789,25 +3789,25 @@
         <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC13" t="n">
         <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
         <v>21</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>6.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4300,7 +4300,7 @@
         <v>9</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
         <v>6.6</v>
@@ -4312,7 +4312,7 @@
         <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="BF15" t="n">
         <v>4.7</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I16" t="n">
         <v>1.82</v>
@@ -4428,52 +4428,52 @@
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
         <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
         <v>2.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
         <v>970</v>
@@ -4494,7 +4494,7 @@
         <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
         <v>500</v>
@@ -4530,7 +4530,7 @@
         <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -4542,49 +4542,49 @@
         <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH16" t="n">
         <v>6</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4611,7 +4611,7 @@
         <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU16" t="n">
         <v>3.15</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -4721,10 +4721,10 @@
         <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -4733,13 +4733,13 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
         <v>42</v>
       </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
@@ -4748,10 +4748,10 @@
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
@@ -4775,52 +4775,52 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="AU17" t="n">
         <v>5.1</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BF17" t="n">
         <v>2.86</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -4924,76 +4924,76 @@
         <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
         <v>2.6</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.72</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
         <v>1.84</v>
       </c>
       <c r="S18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X18" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC18" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>500</v>
@@ -5002,7 +5002,7 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
         <v>500</v>
@@ -5011,7 +5011,7 @@
         <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
         <v>500</v>
@@ -5020,131 +5020,131 @@
         <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G19" t="n">
         <v>1.4</v>
@@ -5190,7 +5190,7 @@
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
@@ -5340,19 +5340,19 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BJ19" t="n">
         <v>22</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BN19" t="n">
         <v>4.2</v>
@@ -5370,25 +5370,25 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BT19" t="n">
         <v>21</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -5483,10 +5483,10 @@
         <v>2.12</v>
       </c>
       <c r="X20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
@@ -5495,13 +5495,13 @@
         <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC20" t="n">
         <v>500</v>
       </c>
       <c r="AD20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
@@ -5510,10 +5510,10 @@
         <v>500</v>
       </c>
       <c r="AG20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH20" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -5537,55 +5537,55 @@
         <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BG20" t="n">
         <v>1.55</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.24</v>
@@ -5707,16 +5707,16 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R21" t="n">
         <v>1.6</v>
@@ -5731,10 +5731,10 @@
         <v>2.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="X21" t="n">
         <v>32</v>
@@ -5755,10 +5755,10 @@
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -5794,13 +5794,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
         <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -5836,7 +5836,7 @@
         <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF21" t="n">
         <v>5.6</v>
@@ -5851,10 +5851,10 @@
         <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5863,10 +5863,10 @@
         <v>10.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP21" t="n">
         <v>10.5</v>
@@ -5881,32 +5881,32 @@
         <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA21" t="n">
         <v>6.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I22" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J22" t="n">
         <v>4.2</v>
@@ -5958,7 +5958,7 @@
         <v>1.21</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
         <v>6.2</v>
@@ -5967,7 +5967,7 @@
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q22" t="n">
         <v>1.46</v>
@@ -6027,7 +6027,7 @@
         <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
         <v>44</v>
@@ -6102,19 +6102,19 @@
         <v>5.1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
         <v>8.199999999999999</v>
@@ -6126,13 +6126,13 @@
         <v>26</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
         <v>29</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
         <v>5.6</v>
@@ -6144,23 +6144,23 @@
         <v>13</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA22" t="n">
         <v>8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G23" t="n">
         <v>1.58</v>
@@ -6203,10 +6203,10 @@
         <v>7.2</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
@@ -6218,25 +6218,25 @@
         <v>5.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
         <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.64</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.68</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
         <v>1.16</v>
@@ -6260,7 +6260,7 @@
         <v>24</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD23" t="n">
         <v>950</v>
@@ -6269,7 +6269,7 @@
         <v>480</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -6284,7 +6284,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -6305,10 +6305,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>9.4</v>
@@ -6320,7 +6320,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX23" t="n">
         <v>9.4</v>
@@ -6332,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
         <v>11</v>
@@ -6344,13 +6344,13 @@
         <v>14.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>4.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN23" t="n">
         <v>4.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -6451,73 +6451,73 @@
         <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="T24" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="U24" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X24" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
@@ -6541,7 +6541,7 @@
         <v>500</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
@@ -6553,7 +6553,7 @@
         <v>38</v>
       </c>
       <c r="AP24" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>12</v>
@@ -6562,25 +6562,25 @@
         <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>10.5</v>
@@ -6589,16 +6589,16 @@
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD24" t="n">
         <v>14.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BF24" t="n">
         <v>12.5</v>
@@ -6607,10 +6607,10 @@
         <v>7.4</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6622,53 +6622,53 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>4.5</v>
       </c>
       <c r="G26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="I26" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.23</v>
@@ -6989,7 +6989,7 @@
         <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S26" t="n">
         <v>2.24</v>
@@ -6998,28 +6998,28 @@
         <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V26" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC26" t="n">
         <v>15</v>
@@ -7034,10 +7034,10 @@
         <v>500</v>
       </c>
       <c r="AG26" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI26" t="n">
         <v>28</v>
@@ -7073,7 +7073,7 @@
         <v>14</v>
       </c>
       <c r="AT26" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
         <v>9.199999999999999</v>
@@ -7085,34 +7085,34 @@
         <v>12</v>
       </c>
       <c r="AX26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BA26" t="n">
         <v>18</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG26" t="n">
         <v>6</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>5.3</v>
       </c>
       <c r="BH26" t="n">
         <v>4.7</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H27" t="n">
         <v>6.8</v>
@@ -7219,10 +7219,10 @@
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K27" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.21</v>
@@ -7252,19 +7252,19 @@
         <v>1.67</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V27" t="n">
         <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Y27" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z27" t="n">
         <v>170</v>
@@ -7273,13 +7273,13 @@
         <v>220</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
         <v>240</v>
@@ -7318,13 +7318,13 @@
         <v>21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT27" t="n">
         <v>9.199999999999999</v>
@@ -7333,22 +7333,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX27" t="n">
         <v>8.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ27" t="n">
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -7360,13 +7360,13 @@
         <v>19.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF27" t="n">
         <v>3.95</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH27" t="n">
         <v>5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G28" t="n">
         <v>2.9</v>
       </c>
       <c r="H28" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I28" t="n">
         <v>3.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
@@ -7488,7 +7488,7 @@
         <v>2.84</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
         <v>1.64</v>
@@ -7623,7 +7623,7 @@
         <v>30</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI28" t="n">
         <v>2.46</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN28" t="n">
         <v>5.8</v>
@@ -7650,13 +7650,13 @@
         <v>24</v>
       </c>
       <c r="BQ28" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>44</v>
       </c>
       <c r="BS28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
         <v>6.4</v>
@@ -7665,26 +7665,26 @@
         <v>5.1</v>
       </c>
       <c r="BV28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX28" t="n">
         <v>46</v>
       </c>
       <c r="BY28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>42</v>
       </c>
       <c r="CA28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
         <v>2.86</v>
@@ -7763,7 +7763,7 @@
         <v>3.15</v>
       </c>
       <c r="V29" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W29" t="n">
         <v>1.53</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
         <v>3.2</v>
@@ -8238,7 +8238,7 @@
         <v>2.92</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
         <v>1.36</v>
@@ -8256,7 +8256,7 @@
         <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -8274,7 +8274,7 @@
         <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
         <v>90</v>
@@ -8325,7 +8325,7 @@
         <v>500</v>
       </c>
       <c r="AN31" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
         <v>500</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -8477,64 +8477,64 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G32" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K32" t="n">
         <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X32" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="Y32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="n">
         <v>32</v>
@@ -8543,79 +8543,79 @@
         <v>80</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AE32" t="n">
         <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
         <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
         <v>55</v>
       </c>
       <c r="AJ32" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="n">
         <v>34</v>
       </c>
       <c r="AM32" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO32" t="n">
         <v>36</v>
       </c>
       <c r="AP32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ32" t="n">
         <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
         <v>38</v>
@@ -8624,25 +8624,25 @@
         <v>21</v>
       </c>
       <c r="BC32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="BF32" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH32" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ32" t="n">
         <v>10.5</v>
@@ -8654,25 +8654,25 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR32" t="n">
         <v>32</v>
       </c>
       <c r="BS32" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BT32" t="n">
         <v>8.6</v>
@@ -8684,13 +8684,13 @@
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BZ32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
         <v>1.94</v>
       </c>
       <c r="W33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X33" t="n">
         <v>36</v>
@@ -8875,7 +8875,7 @@
         <v>17</v>
       </c>
       <c r="BB33" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="BC33" t="n">
         <v>24</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>2.68</v>
       </c>
       <c r="H34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
         <v>3.4</v>
@@ -9030,7 +9030,7 @@
         <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V34" t="n">
         <v>1.41</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G35" t="n">
         <v>2.54</v>
@@ -9254,7 +9254,7 @@
         <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.6</v>
@@ -9266,7 +9266,7 @@
         <v>2.22</v>
       </c>
       <c r="O35" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P35" t="n">
         <v>1.41</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K36" t="n">
         <v>3.35</v>
@@ -9577,7 +9577,7 @@
         <v>36</v>
       </c>
       <c r="AH36" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI36" t="n">
         <v>500</v>
@@ -9592,7 +9592,7 @@
         <v>500</v>
       </c>
       <c r="AM36" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
         <v>500</v>
@@ -9604,13 +9604,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -9619,10 +9619,10 @@
         <v>5.7</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="AX36" t="n">
         <v>8</v>
@@ -9631,34 +9631,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="BE36" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="BF36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BH36" t="n">
         <v>3.05</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>7.2</v>
       </c>
       <c r="H37" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I37" t="n">
         <v>1.73</v>
@@ -9762,7 +9762,7 @@
         <v>3.55</v>
       </c>
       <c r="K37" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
         <v>1.44</v>
@@ -9918,7 +9918,7 @@
         <v>12.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9933,13 +9933,13 @@
         <v>5</v>
       </c>
       <c r="BP37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
         <v>8.4</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS37" t="n">
         <v>8.6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G38" t="n">
         <v>1.63</v>
@@ -10013,7 +10013,7 @@
         <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>4.2</v>
@@ -10040,7 +10040,7 @@
         <v>1.19</v>
       </c>
       <c r="S38" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
         <v>2.54</v>
@@ -10058,7 +10058,7 @@
         <v>970</v>
       </c>
       <c r="Y38" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Z38" t="n">
         <v>100</v>
@@ -10073,7 +10073,7 @@
         <v>16.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE38" t="n">
         <v>1000</v>
@@ -10085,7 +10085,7 @@
         <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G39" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H39" t="n">
         <v>5.3</v>
       </c>
       <c r="I39" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.57</v>
@@ -10303,7 +10303,7 @@
         <v>1.61</v>
       </c>
       <c r="V39" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
         <v>2.02</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
         <v>3.05</v>
       </c>
       <c r="O40" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P40" t="n">
         <v>1.77</v>
@@ -10563,10 +10563,10 @@
         <v>1.44</v>
       </c>
       <c r="X40" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y40" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z40" t="n">
         <v>500</v>
@@ -10575,13 +10575,13 @@
         <v>900</v>
       </c>
       <c r="AB40" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC40" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD40" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE40" t="n">
         <v>500</v>
@@ -10590,10 +10590,10 @@
         <v>500</v>
       </c>
       <c r="AG40" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH40" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI40" t="n">
         <v>500</v>
@@ -10617,58 +10617,58 @@
         <v>500</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -10763,64 +10763,64 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G41" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H41" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
         <v>12</v>
       </c>
       <c r="J41" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P41" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="S41" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="T41" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>1.09</v>
       </c>
       <c r="W41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="X41" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y41" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Z41" t="n">
         <v>120</v>
@@ -10829,16 +10829,16 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD41" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AE41" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AF41" t="n">
         <v>11</v>
@@ -10847,82 +10847,82 @@
         <v>13</v>
       </c>
       <c r="AH41" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI41" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ41" t="n">
         <v>13</v>
       </c>
       <c r="AK41" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AL41" t="n">
         <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN41" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AO41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP41" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
         <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -11017,166 +11017,166 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="G42" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="H42" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="K42" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="P42" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="R42" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="S42" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V42" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W42" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB42" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF42" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ42" t="n">
-        <v>900</v>
+        <v>19.5</v>
       </c>
       <c r="AK42" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN42" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.08</v>
+        <v>9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.08</v>
+        <v>23</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.08</v>
+        <v>9.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.06</v>
+        <v>9</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.08</v>
+        <v>8</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.08</v>
+        <v>10</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.08</v>
+        <v>7.8</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.08</v>
+        <v>7.2</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.08</v>
+        <v>9.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.08</v>
+        <v>8.4</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.07</v>
+        <v>7.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.08</v>
+        <v>7.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.08</v>
+        <v>9.6</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
         <v>1.19</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q43" t="n">
         <v>1.5</v>
@@ -11325,13 +11325,13 @@
         <v>1.23</v>
       </c>
       <c r="X43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y43" t="n">
         <v>13</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA43" t="n">
         <v>23</v>
@@ -11340,7 +11340,7 @@
         <v>23</v>
       </c>
       <c r="AC43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD43" t="n">
         <v>11.5</v>
@@ -11349,88 +11349,88 @@
         <v>20</v>
       </c>
       <c r="AF43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ43" t="n">
         <v>900</v>
       </c>
       <c r="AK43" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL43" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM43" t="n">
         <v>85</v>
       </c>
       <c r="AN43" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX43" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY43" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB43" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BH43" t="n">
         <v>4.4</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G44" t="n">
         <v>3.15</v>
@@ -11534,22 +11534,22 @@
         <v>2.36</v>
       </c>
       <c r="I44" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K44" t="n">
         <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M44" t="n">
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O44" t="n">
         <v>1.24</v>
@@ -11558,22 +11558,22 @@
         <v>2.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R44" t="n">
         <v>1.49</v>
       </c>
       <c r="S44" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T44" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U44" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V44" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W44" t="n">
         <v>1.46</v>
@@ -11600,7 +11600,7 @@
         <v>14</v>
       </c>
       <c r="AE44" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF44" t="n">
         <v>26</v>
@@ -11612,22 +11612,22 @@
         <v>17.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AJ44" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK44" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL44" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM44" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN44" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO44" t="n">
         <v>18</v>
@@ -11642,7 +11642,7 @@
         <v>13.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AT44" t="n">
         <v>11.5</v>
@@ -11666,19 +11666,19 @@
         <v>12</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BF44" t="n">
         <v>19</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G45" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I45" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J45" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.3</v>
@@ -11803,25 +11803,25 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>1.27</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
         <v>1.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U45" t="n">
         <v>2.38</v>
@@ -11830,7 +11830,7 @@
         <v>1.54</v>
       </c>
       <c r="W45" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X45" t="n">
         <v>18</v>
@@ -11848,7 +11848,7 @@
         <v>14</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD45" t="n">
         <v>13</v>
@@ -11860,22 +11860,22 @@
         <v>24</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH45" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="n">
         <v>34</v>
       </c>
       <c r="AL45" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
@@ -11896,7 +11896,7 @@
         <v>13.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AT45" t="n">
         <v>11</v>
@@ -11923,16 +11923,16 @@
         <v>30</v>
       </c>
       <c r="BB45" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BC45" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD45" t="n">
         <v>27</v>
       </c>
       <c r="BE45" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF45" t="n">
         <v>16.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -12111,13 +12111,13 @@
         <v>500</v>
       </c>
       <c r="AF46" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG46" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AH46" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI46" t="n">
         <v>500</v>
@@ -12147,22 +12147,22 @@
         <v>7.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT46" t="n">
         <v>6.2</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV46" t="n">
         <v>11</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX46" t="n">
         <v>11.5</v>
@@ -12171,28 +12171,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB46" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF46" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH46" t="n">
         <v>2.92</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>11.5</v>
       </c>
       <c r="J47" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
         <v>7.4</v>
@@ -12329,7 +12329,7 @@
         <v>1.94</v>
       </c>
       <c r="T47" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U47" t="n">
         <v>2.08</v>
@@ -12341,7 +12341,7 @@
         <v>3.75</v>
       </c>
       <c r="X47" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="Y47" t="n">
         <v>60</v>
@@ -12374,7 +12374,7 @@
         <v>32</v>
       </c>
       <c r="AI47" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AJ47" t="n">
         <v>14</v>
@@ -12386,7 +12386,7 @@
         <v>32</v>
       </c>
       <c r="AM47" t="n">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="AN47" t="n">
         <v>3.9</v>
@@ -12395,16 +12395,16 @@
         <v>130</v>
       </c>
       <c r="AP47" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT47" t="n">
         <v>10.5</v>
@@ -12413,10 +12413,10 @@
         <v>12</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AW47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX47" t="n">
         <v>7.8</v>
@@ -12428,7 +12428,7 @@
         <v>19</v>
       </c>
       <c r="BA47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB47" t="n">
         <v>9.800000000000001</v>
@@ -12440,13 +12440,13 @@
         <v>21</v>
       </c>
       <c r="BE47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF47" t="n">
         <v>3.3</v>
       </c>
       <c r="BG47" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BH47" t="n">
         <v>5.5</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -12559,13 +12559,13 @@
         <v>3.45</v>
       </c>
       <c r="L48" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O48" t="n">
         <v>1.42</v>
@@ -12574,16 +12574,16 @@
         <v>1.62</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R48" t="n">
         <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T48" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U48" t="n">
         <v>1.89</v>
@@ -12595,7 +12595,7 @@
         <v>1.48</v>
       </c>
       <c r="X48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
         <v>12</v>
@@ -12622,10 +12622,10 @@
         <v>500</v>
       </c>
       <c r="AG48" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AH48" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI48" t="n">
         <v>500</v>
@@ -12652,73 +12652,73 @@
         <v>7.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.92</v>
+        <v>5.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF48" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF48" t="n">
-        <v>4</v>
-      </c>
       <c r="BG48" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH48" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
@@ -12730,13 +12730,13 @@
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
@@ -12748,23 +12748,23 @@
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
         <v>2.06</v>
       </c>
       <c r="H49" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
         <v>6.6</v>
@@ -12828,13 +12828,13 @@
         <v>1.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R49" t="n">
         <v>1.16</v>
       </c>
       <c r="S49" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="T49" t="n">
         <v>2.24</v>
@@ -12864,10 +12864,10 @@
         <v>27</v>
       </c>
       <c r="AC49" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE49" t="n">
         <v>700</v>
@@ -12879,7 +12879,7 @@
         <v>500</v>
       </c>
       <c r="AH49" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI49" t="n">
         <v>700</v>
@@ -12909,22 +12909,22 @@
         <v>10</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="AT49" t="n">
         <v>4.7</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AV49" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="AX49" t="n">
         <v>7.6</v>
@@ -12933,28 +12933,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BB49" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC49" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>6</v>
+        <v>2.44</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G50" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H50" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K50" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O50" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="P50" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q50" t="n">
         <v>2.74</v>
@@ -13097,16 +13097,16 @@
         <v>1.11</v>
       </c>
       <c r="V50" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W50" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z50" t="n">
         <v>500</v>
@@ -13115,13 +13115,13 @@
         <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE50" t="n">
         <v>700</v>
@@ -13130,10 +13130,10 @@
         <v>500</v>
       </c>
       <c r="AG50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH50" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI50" t="n">
         <v>700</v>
@@ -13157,58 +13157,58 @@
         <v>700</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
         <v>500</v>
       </c>
       <c r="AB51" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC51" t="n">
         <v>8</v>
@@ -13414,13 +13414,13 @@
         <v>5.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR51" t="n">
         <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT51" t="n">
         <v>5.7</v>
@@ -13432,7 +13432,7 @@
         <v>12.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX51" t="n">
         <v>12.5</v>
@@ -13444,25 +13444,25 @@
         <v>21</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB51" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -13560,19 +13560,19 @@
         <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H52" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I52" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="K52" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13590,7 +13590,7 @@
         <v>3.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="R52" t="n">
         <v>2.04</v>
@@ -13611,10 +13611,10 @@
         <v>1.01</v>
       </c>
       <c r="X52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z52" t="n">
         <v>500</v>
@@ -13623,13 +13623,13 @@
         <v>900</v>
       </c>
       <c r="AB52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE52" t="n">
         <v>500</v>
@@ -13638,10 +13638,10 @@
         <v>500</v>
       </c>
       <c r="AG52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH52" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI52" t="n">
         <v>500</v>
@@ -13665,58 +13665,58 @@
         <v>500</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BC52" t="n">
         <v>1.03</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13844,7 @@
         <v>3.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R53" t="n">
         <v>1.46</v>
@@ -13877,7 +13877,7 @@
         <v>1000</v>
       </c>
       <c r="AB53" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC53" t="n">
         <v>1000</v>
@@ -13889,10 +13889,10 @@
         <v>1000</v>
       </c>
       <c r="AF53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG53" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH53" t="n">
         <v>1000</v>
@@ -13901,19 +13901,19 @@
         <v>1000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM53" t="n">
         <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G54" t="n">
         <v>2.96</v>
@@ -14080,7 +14080,7 @@
         <v>4.2</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,25 +14089,25 @@
         <v>1.02</v>
       </c>
       <c r="N54" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
         <v>1.1</v>
       </c>
       <c r="P54" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="R54" t="n">
         <v>1.86</v>
       </c>
       <c r="S54" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="T54" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U54" t="n">
         <v>1.11</v>
@@ -14119,10 +14119,10 @@
         <v>1.51</v>
       </c>
       <c r="X54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z54" t="n">
         <v>500</v>
@@ -14131,13 +14131,13 @@
         <v>900</v>
       </c>
       <c r="AB54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE54" t="n">
         <v>500</v>
@@ -14146,10 +14146,10 @@
         <v>500</v>
       </c>
       <c r="AG54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH54" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI54" t="n">
         <v>500</v>
@@ -14221,10 +14221,10 @@
         <v>1.03</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -14319,10 +14319,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G55" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H55" t="n">
         <v>3.6</v>
@@ -14370,7 +14370,7 @@
         <v>1.3</v>
       </c>
       <c r="W55" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X55" t="n">
         <v>950</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -14839,10 +14839,10 @@
         <v>3.55</v>
       </c>
       <c r="J57" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K57" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L57" t="n">
         <v>1.4</v>
@@ -14863,7 +14863,7 @@
         <v>2.2</v>
       </c>
       <c r="R57" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
         <v>4.2</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
         <v>5.1</v>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -15126,7 +15126,7 @@
         <v>2.34</v>
       </c>
       <c r="U58" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V58" t="n">
         <v>1.21</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
         <v>6.4</v>
       </c>
       <c r="O59" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P59" t="n">
         <v>2.86</v>
@@ -15386,10 +15386,10 @@
         <v>2.42</v>
       </c>
       <c r="W59" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X59" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y59" t="n">
         <v>19</v>
@@ -15401,7 +15401,7 @@
         <v>970</v>
       </c>
       <c r="AB59" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC59" t="n">
         <v>970</v>
@@ -15416,7 +15416,7 @@
         <v>500</v>
       </c>
       <c r="AG59" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH59" t="n">
         <v>970</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -15595,13 +15595,13 @@
         <v>1.71</v>
       </c>
       <c r="H60" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I60" t="n">
         <v>5.5</v>
       </c>
       <c r="J60" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K60" t="n">
         <v>5.5</v>
@@ -15640,7 +15640,7 @@
         <v>1.22</v>
       </c>
       <c r="W60" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X60" t="n">
         <v>950</v>
@@ -15748,13 +15748,13 @@
         <v>4.1</v>
       </c>
       <c r="BG60" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BH60" t="n">
         <v>5.6</v>
       </c>
       <c r="BI60" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -15891,13 +15891,13 @@
         <v>2.42</v>
       </c>
       <c r="V61" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="W61" t="n">
         <v>1.15</v>
       </c>
       <c r="X61" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Y61" t="n">
         <v>970</v>
@@ -15909,7 +15909,7 @@
         <v>970</v>
       </c>
       <c r="AB61" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AC61" t="n">
         <v>970</v>
@@ -15924,10 +15924,10 @@
         <v>75</v>
       </c>
       <c r="AG61" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AH61" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI61" t="n">
         <v>500</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -16097,22 +16097,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H62" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I62" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L62" t="n">
         <v>1.46</v>
@@ -16133,22 +16133,22 @@
         <v>2.6</v>
       </c>
       <c r="R62" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S62" t="n">
         <v>5.4</v>
       </c>
       <c r="T62" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U62" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V62" t="n">
         <v>1.41</v>
       </c>
       <c r="W62" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X62" t="n">
         <v>10</v>
@@ -16178,7 +16178,7 @@
         <v>18</v>
       </c>
       <c r="AG62" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH62" t="n">
         <v>26</v>
@@ -16214,19 +16214,19 @@
         <v>17</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT62" t="n">
         <v>6.4</v>
       </c>
       <c r="AU62" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV62" t="n">
         <v>11</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX62" t="n">
         <v>12.5</v>
@@ -16235,28 +16235,28 @@
         <v>10</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB62" t="n">
         <v>5.4</v>
       </c>
       <c r="BC62" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD62" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF62" t="n">
         <v>5.5</v>
       </c>
-      <c r="BE62" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG62" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -16366,10 +16366,10 @@
         <v>2.8</v>
       </c>
       <c r="K63" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
@@ -16387,7 +16387,7 @@
         <v>2.32</v>
       </c>
       <c r="R63" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S63" t="n">
         <v>2.78</v>
@@ -16405,10 +16405,10 @@
         <v>1.4</v>
       </c>
       <c r="X63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z63" t="n">
         <v>500</v>
@@ -16417,13 +16417,13 @@
         <v>900</v>
       </c>
       <c r="AB63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE63" t="n">
         <v>500</v>
@@ -16432,10 +16432,10 @@
         <v>500</v>
       </c>
       <c r="AG63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH63" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI63" t="n">
         <v>500</v>
@@ -16462,55 +16462,55 @@
         <v>1.03</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G64" t="n">
         <v>2.74</v>
@@ -16614,10 +16614,10 @@
         <v>3.1</v>
       </c>
       <c r="I64" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J64" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K64" t="n">
         <v>3.6</v>
@@ -16629,22 +16629,22 @@
         <v>1.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>1.42</v>
       </c>
       <c r="P64" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R64" t="n">
         <v>1.22</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T64" t="n">
         <v>1.89</v>
@@ -16689,7 +16689,7 @@
         <v>970</v>
       </c>
       <c r="AH64" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI64" t="n">
         <v>500</v>
@@ -16713,64 +16713,64 @@
         <v>500</v>
       </c>
       <c r="AP64" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AR64" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AU64" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV64" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW64" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="AX64" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AY64" t="n">
         <v>3.8</v>
       </c>
       <c r="AZ64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB64" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA64" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BC64" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="BD64" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="BE64" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BF64" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="BG64" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="BH64" t="n">
         <v>4.7</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -16859,16 +16859,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G65" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
@@ -16886,28 +16886,28 @@
         <v>3.05</v>
       </c>
       <c r="O65" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P65" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R65" t="n">
         <v>1.25</v>
       </c>
       <c r="S65" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U65" t="n">
         <v>1.91</v>
       </c>
       <c r="V65" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W65" t="n">
         <v>1.58</v>
@@ -16919,19 +16919,19 @@
         <v>12</v>
       </c>
       <c r="Z65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA65" t="n">
         <v>70</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC65" t="n">
         <v>8</v>
       </c>
       <c r="AD65" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE65" t="n">
         <v>55</v>
@@ -16961,64 +16961,64 @@
         <v>150</v>
       </c>
       <c r="AN65" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO65" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP65" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ65" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR65" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AS65" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW65" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT65" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AX65" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY65" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ65" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="BA65" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD65" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB65" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE65" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF65" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG65" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH65" t="n">
         <v>3.2</v>
@@ -17030,16 +17030,16 @@
         <v>11</v>
       </c>
       <c r="BK65" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN65" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO65" t="n">
         <v>4</v>
@@ -17048,7 +17048,7 @@
         <v>21</v>
       </c>
       <c r="BQ65" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR65" t="n">
         <v>40</v>
@@ -17066,23 +17066,23 @@
         <v>32</v>
       </c>
       <c r="BW65" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX65" t="n">
         <v>48</v>
       </c>
       <c r="BY65" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ65" t="n">
         <v>38</v>
       </c>
       <c r="CA65" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -17113,52 +17113,52 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="H66" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I66" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K66" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="L66" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M66" t="n">
         <v>1.02</v>
       </c>
       <c r="N66" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P66" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="Q66" t="n">
         <v>1.33</v>
       </c>
       <c r="R66" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="T66" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="U66" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="V66" t="n">
         <v>1.01</v>
@@ -17167,28 +17167,28 @@
         <v>1.01</v>
       </c>
       <c r="X66" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="Y66" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="n">
         <v>25</v>
       </c>
       <c r="AA66" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AB66" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AC66" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AD66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE66" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>22</v>
       </c>
       <c r="AF66" t="n">
         <v>500</v>
@@ -17197,19 +17197,19 @@
         <v>28</v>
       </c>
       <c r="AH66" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AI66" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AJ66" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK66" t="n">
         <v>500</v>
       </c>
       <c r="AL66" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM66" t="n">
         <v>500</v>
@@ -17218,16 +17218,16 @@
         <v>30</v>
       </c>
       <c r="AO66" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.88</v>
+        <v>9.4</v>
       </c>
       <c r="AQ66" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AR66" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AS66" t="n">
         <v>13.5</v>
@@ -17236,97 +17236,97 @@
         <v>20</v>
       </c>
       <c r="AU66" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AV66" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AW66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB66" t="n">
         <v>10</v>
       </c>
-      <c r="AX66" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BC66" t="n">
-        <v>2.76</v>
+        <v>24</v>
       </c>
       <c r="BD66" t="n">
-        <v>2.74</v>
+        <v>22</v>
       </c>
       <c r="BE66" t="n">
-        <v>2.78</v>
+        <v>27</v>
       </c>
       <c r="BF66" t="n">
         <v>14</v>
       </c>
       <c r="BG66" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BH66" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI66" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="BJ66" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK66" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
       </c>
       <c r="BM66" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="BN66" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO66" t="n">
-        <v>1.91</v>
+        <v>5.3</v>
       </c>
       <c r="BP66" t="n">
         <v>38</v>
       </c>
       <c r="BQ66" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="BR66" t="n">
         <v>38</v>
       </c>
       <c r="BS66" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="BT66" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BU66" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BV66" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BW66" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BX66" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BY66" t="n">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="BZ66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G67" t="n">
         <v>2.1</v>
@@ -17391,7 +17391,7 @@
         <v>1.13</v>
       </c>
       <c r="N67" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O67" t="n">
         <v>1.58</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -17624,13 +17624,13 @@
         <v>2.18</v>
       </c>
       <c r="G68" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H68" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I68" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>3.15</v>
@@ -17645,7 +17645,7 @@
         <v>1.12</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O68" t="n">
         <v>1.52</v>
@@ -17672,10 +17672,10 @@
         <v>1.31</v>
       </c>
       <c r="W68" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X68" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y68" t="n">
         <v>12.5</v>
@@ -17738,10 +17738,10 @@
         <v>20</v>
       </c>
       <c r="AS68" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT68" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU68" t="n">
         <v>6.4</v>
@@ -17750,7 +17750,7 @@
         <v>14.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX68" t="n">
         <v>10</v>
@@ -17762,25 +17762,25 @@
         <v>20</v>
       </c>
       <c r="BA68" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB68" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG68" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG68" t="n">
-        <v>7</v>
       </c>
       <c r="BH68" t="n">
         <v>2.86</v>
@@ -17810,13 +17810,13 @@
         <v>20</v>
       </c>
       <c r="BQ68" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR68" t="n">
         <v>46</v>
       </c>
       <c r="BS68" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT68" t="n">
         <v>7.2</v>
@@ -17825,13 +17825,13 @@
         <v>6</v>
       </c>
       <c r="BV68" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW68" t="n">
         <v>9</v>
       </c>
       <c r="BX68" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY68" t="n">
         <v>9.800000000000001</v>
@@ -17840,11 +17840,11 @@
         <v>1000</v>
       </c>
       <c r="CA68" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G69" t="n">
         <v>2.3</v>
@@ -17923,16 +17923,16 @@
         <v>1.11</v>
       </c>
       <c r="V69" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W69" t="n">
         <v>1.76</v>
       </c>
       <c r="X69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z69" t="n">
         <v>500</v>
@@ -17941,13 +17941,13 @@
         <v>900</v>
       </c>
       <c r="AB69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE69" t="n">
         <v>500</v>
@@ -17956,10 +17956,10 @@
         <v>500</v>
       </c>
       <c r="AG69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH69" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI69" t="n">
         <v>500</v>
@@ -17983,58 +17983,58 @@
         <v>500</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY69" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC69" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE69" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF69" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG69" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH69" t="n">
         <v>3.05</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -857,85 +857,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
         <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -944,37 +944,37 @@
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK2" t="n">
         <v>19</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -986,101 +986,101 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>55</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>1.74</v>
       </c>
       <c r="I4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J4" t="n">
         <v>3.8</v>
@@ -1389,19 +1389,19 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
         <v>1.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
         <v>3.1</v>
@@ -1410,13 +1410,13 @@
         <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>2.14</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1425,7 +1425,7 @@
         <v>9.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
@@ -1440,7 +1440,7 @@
         <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>44</v>
@@ -1473,7 +1473,7 @@
         <v>12</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>7.8</v>
@@ -1482,7 +1482,7 @@
         <v>8.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT4" t="n">
         <v>15.5</v>
@@ -1494,31 +1494,31 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
         <v>29</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE4" t="n">
         <v>9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>8.6</v>
@@ -1536,22 +1536,22 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BQ4" t="n">
         <v>9</v>
@@ -1560,7 +1560,7 @@
         <v>55</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT4" t="n">
         <v>4.6</v>
@@ -1572,13 +1572,13 @@
         <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
         <v>2.78</v>
@@ -1634,7 +1634,7 @@
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.2</v>
@@ -1646,22 +1646,22 @@
         <v>6.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>1.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U5" t="n">
         <v>3.05</v>
@@ -1670,7 +1670,7 @@
         <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1685,10 +1685,10 @@
         <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1727,7 +1727,7 @@
         <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
@@ -1736,7 +1736,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
@@ -1751,7 +1751,7 @@
         <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AY5" t="n">
         <v>7.6</v>
@@ -1760,19 +1760,19 @@
         <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
         <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
         <v>7.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
         <v>3.6</v>
@@ -1981,19 +1981,19 @@
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
@@ -2002,10 +2002,10 @@
         <v>6.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
         <v>8.4</v>
@@ -2014,19 +2014,19 @@
         <v>8.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="BF6" t="n">
         <v>3.65</v>
@@ -2035,7 +2035,7 @@
         <v>4.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI6" t="n">
         <v>3.7</v>
@@ -2074,7 +2074,7 @@
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
@@ -2157,7 +2157,7 @@
         <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
         <v>2.04</v>
@@ -2184,7 +2184,7 @@
         <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>16</v>
@@ -2199,7 +2199,7 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>65</v>
@@ -2250,7 +2250,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
@@ -2259,13 +2259,13 @@
         <v>9.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
         <v>8.199999999999999</v>
@@ -2280,7 +2280,7 @@
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
         <v>8.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
         <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
@@ -2444,34 +2444,34 @@
         <v>100</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
         <v>970</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
@@ -2483,73 +2483,73 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
         <v>6.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI8" t="n">
         <v>3.35</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK8" t="n">
         <v>4.9</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.68</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.59</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.92</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
         <v>2.9</v>
@@ -2644,7 +2644,7 @@
         <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2668,7 +2668,7 @@
         <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -2686,7 +2686,7 @@
         <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2752,7 +2752,7 @@
         <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6.4</v>
@@ -2764,7 +2764,7 @@
         <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2773,28 +2773,28 @@
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BF9" t="n">
         <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.65</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>2.94</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2931,7 +2931,7 @@
         <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
         <v>2.46</v>
@@ -3045,7 +3045,7 @@
         <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
         <v>6.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>1.86</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.25</v>
@@ -3167,28 +3167,28 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
         <v>1.95</v>
@@ -3203,7 +3203,7 @@
         <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
@@ -3212,97 +3212,97 @@
         <v>950</v>
       </c>
       <c r="AC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH11" t="n">
         <v>970</v>
       </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
       <c r="AI11" t="n">
         <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="AK11" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AL11" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.72</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.59</v>
+        <v>7.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.67</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.76</v>
+        <v>5.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.65</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.72</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.76</v>
+        <v>3.95</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.77</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
         <v>4.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3427,34 +3427,34 @@
         <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
         <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>36</v>
@@ -3463,7 +3463,7 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
         <v>8.800000000000001</v>
@@ -3478,7 +3478,7 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>20</v>
@@ -3487,130 +3487,130 @@
         <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>140</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
         <v>18.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.08</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
         <v>3.45</v>
@@ -3663,55 +3663,55 @@
         <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
         <v>25</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -3720,19 +3720,19 @@
         <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
         <v>19.5</v>
@@ -3741,7 +3741,7 @@
         <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
@@ -3759,70 +3759,70 @@
         <v>36</v>
       </c>
       <c r="AP13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BB13" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
         <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BF13" t="n">
         <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
         <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.86</v>
@@ -3923,7 +3923,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,28 +3935,28 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
         <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
         <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V14" t="n">
         <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
         <v>32</v>
@@ -4013,16 +4013,16 @@
         <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
         <v>14</v>
@@ -4031,31 +4031,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="BC14" t="n">
         <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
         <v>20</v>
@@ -4064,7 +4064,7 @@
         <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
         <v>2.66</v>
@@ -4168,10 +4168,10 @@
         <v>2.82</v>
       </c>
       <c r="I15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
@@ -4213,7 +4213,7 @@
         <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
@@ -4261,10 +4261,10 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
         <v>8.4</v>
@@ -4273,10 +4273,10 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4288,7 +4288,7 @@
         <v>8.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
@@ -4297,25 +4297,25 @@
         <v>6.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
         <v>6.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -4413,70 +4413,70 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="I16" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>970</v>
@@ -4488,7 +4488,7 @@
         <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AF16" t="n">
         <v>500</v>
@@ -4497,7 +4497,7 @@
         <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4521,7 +4521,7 @@
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
         <v>5.4</v>
@@ -4530,113 +4530,113 @@
         <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
         <v>5.2</v>
       </c>
-      <c r="BH16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>5.1</v>
       </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>950</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -4667,230 +4667,230 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.34</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>500</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="R17" t="n">
         <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
         <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.92</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.86</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.94</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.99</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.85</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.95</v>
+        <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.92</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.83</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.94</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.97</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.93</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.93</v>
+        <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.98</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.86</v>
+        <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.65</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.18</v>
@@ -4966,7 +4966,7 @@
         <v>1.39</v>
       </c>
       <c r="U18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V18" t="n">
         <v>1.48</v>
@@ -5029,19 +5029,19 @@
         <v>55</v>
       </c>
       <c r="AP18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR18" t="n">
         <v>6</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
         <v>8.800000000000001</v>
@@ -5050,10 +5050,10 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY18" t="n">
         <v>9.6</v>
@@ -5062,22 +5062,22 @@
         <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD18" t="n">
         <v>6</v>
       </c>
-      <c r="BC18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG18" t="n">
         <v>4.8</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -5175,49 +5175,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
         <v>4.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U19" t="n">
         <v>1.45</v>
@@ -5226,169 +5226,169 @@
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="X19" t="n">
         <v>11.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z19" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>350</v>
+        <v>65</v>
       </c>
       <c r="AE19" t="n">
-        <v>550</v>
+        <v>490</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AI19" t="n">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
         <v>4.3</v>
       </c>
       <c r="AU19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>9</v>
       </c>
-      <c r="AV19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BG19" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="BJ19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.73</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="BP19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.81</v>
+        <v>6.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -5429,230 +5429,230 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV20" t="n">
         <v>16.5</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AW20" t="n">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.21</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.23</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.23</v>
+        <v>16.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.22</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I22" t="n">
         <v>1.95</v>
@@ -5958,7 +5958,7 @@
         <v>1.21</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
         <v>6.2</v>
@@ -5967,7 +5967,7 @@
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
         <v>1.46</v>
@@ -5982,7 +5982,7 @@
         <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V22" t="n">
         <v>2.04</v>
@@ -6006,7 +6006,7 @@
         <v>29</v>
       </c>
       <c r="AC22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>14</v>
@@ -6045,55 +6045,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AX22" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="AY22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>13</v>
       </c>
-      <c r="AX22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>11</v>
-      </c>
       <c r="BA22" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BG22" t="n">
         <v>6.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>5.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -6224,7 +6224,7 @@
         <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R23" t="n">
         <v>1.65</v>
@@ -6233,10 +6233,10 @@
         <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.16</v>
@@ -6293,25 +6293,25 @@
         <v>320</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>170</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
         <v>9.199999999999999</v>
@@ -6323,40 +6323,40 @@
         <v>9</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="BA23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
         <v>9</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN23" t="n">
         <v>4.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I24" t="n">
         <v>2.3</v>
@@ -6460,7 +6460,7 @@
         <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.21</v>
@@ -6469,28 +6469,28 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S24" t="n">
         <v>2.12</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U24" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.76</v>
@@ -6502,13 +6502,13 @@
         <v>950</v>
       </c>
       <c r="Y24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="n">
         <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
         <v>950</v>
@@ -6520,7 +6520,7 @@
         <v>24</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF24" t="n">
         <v>500</v>
@@ -6553,10 +6553,10 @@
         <v>38</v>
       </c>
       <c r="AP24" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
         <v>13.5</v>
@@ -6565,7 +6565,7 @@
         <v>9.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
@@ -6589,7 +6589,7 @@
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC24" t="n">
         <v>9.199999999999999</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>2.06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
         <v>3.85</v>
@@ -6717,34 +6717,34 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.68</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.12</v>
       </c>
       <c r="V25" t="n">
         <v>1.35</v>
@@ -6810,7 +6810,7 @@
         <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>16</v>
@@ -6822,7 +6822,7 @@
         <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
@@ -6834,22 +6834,22 @@
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
         <v>11</v>
       </c>
       <c r="BA25" t="n">
-        <v>18</v>
+        <v>3.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BE25" t="n">
         <v>3.95</v>
@@ -6861,13 +6861,13 @@
         <v>17.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK25" t="n">
         <v>5.3</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.86</v>
+        <v>11.5</v>
       </c>
       <c r="BN25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT25" t="n">
         <v>7.6</v>
       </c>
-      <c r="BO25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BU25" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV25" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BW25" t="n">
-        <v>2.72</v>
+        <v>9</v>
       </c>
       <c r="BX25" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BY25" t="n">
-        <v>2.76</v>
+        <v>9.6</v>
       </c>
       <c r="BZ25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>5.1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I26" t="n">
         <v>1.79</v>
@@ -6971,7 +6971,7 @@
         <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -6983,22 +6983,22 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
         <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
         <v>2.24</v>
       </c>
       <c r="T26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U26" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V26" t="n">
         <v>2.26</v>
@@ -7022,7 +7022,7 @@
         <v>950</v>
       </c>
       <c r="AC26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD26" t="n">
         <v>12</v>
@@ -7061,55 +7061,55 @@
         <v>7.4</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
         <v>6</v>
@@ -7118,40 +7118,40 @@
         <v>4.7</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ26" t="n">
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN26" t="n">
         <v>8.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU26" t="n">
         <v>3.95</v>
@@ -7160,23 +7160,23 @@
         <v>11</v>
       </c>
       <c r="BW26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ26" t="n">
         <v>13</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
         <v>5.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
@@ -7237,19 +7237,19 @@
         <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U27" t="n">
         <v>2.24</v>
@@ -7258,7 +7258,7 @@
         <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="X27" t="n">
         <v>950</v>
@@ -7273,7 +7273,7 @@
         <v>220</v>
       </c>
       <c r="AB27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
         <v>13</v>
@@ -7288,7 +7288,7 @@
         <v>14</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
         <v>42</v>
@@ -7309,82 +7309,82 @@
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO27" t="n">
         <v>90</v>
       </c>
       <c r="AP27" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY27" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>19.5</v>
+        <v>9.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN27" t="n">
         <v>4.6</v>
@@ -7396,41 +7396,41 @@
         <v>9</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT27" t="n">
         <v>11.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>8</v>
       </c>
       <c r="BZ27" t="n">
         <v>11.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -7470,16 +7470,16 @@
         <v>2.96</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K28" t="n">
         <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
@@ -7488,7 +7488,7 @@
         <v>2.84</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
         <v>1.64</v>
@@ -7509,10 +7509,10 @@
         <v>1.91</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
@@ -7560,7 +7560,7 @@
         <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
         <v>38</v>
@@ -7569,16 +7569,16 @@
         <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
@@ -7590,7 +7590,7 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AX28" t="n">
         <v>13.5</v>
@@ -7599,10 +7599,10 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BB28" t="n">
         <v>34</v>
@@ -7623,7 +7623,7 @@
         <v>30</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI28" t="n">
         <v>2.46</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28" t="n">
         <v>5.8</v>
@@ -7650,13 +7650,13 @@
         <v>24</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR28" t="n">
         <v>44</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT28" t="n">
         <v>6.4</v>
@@ -7665,26 +7665,26 @@
         <v>5.1</v>
       </c>
       <c r="BV28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX28" t="n">
         <v>46</v>
       </c>
       <c r="BY28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ28" t="n">
         <v>42</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="G29" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H29" t="n">
         <v>2.34</v>
       </c>
       <c r="I29" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J29" t="n">
         <v>4.2</v>
@@ -7733,13 +7733,13 @@
         <v>4.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M29" t="n">
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>1.11</v>
@@ -7763,13 +7763,13 @@
         <v>3.15</v>
       </c>
       <c r="V29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X29" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y29" t="n">
         <v>25</v>
@@ -7784,7 +7784,7 @@
         <v>26</v>
       </c>
       <c r="AC29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD29" t="n">
         <v>14</v>
@@ -7820,61 +7820,61 @@
         <v>12.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
         <v>17.5</v>
       </c>
       <c r="AR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS29" t="n">
         <v>18.5</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
         <v>18</v>
       </c>
-      <c r="AT29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE29" t="n">
         <v>28</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH29" t="n">
         <v>5.9</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -7969,178 +7969,178 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="G30" t="n">
         <v>1.73</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
         <v>2.38</v>
       </c>
       <c r="X30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
         <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AA30" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE30" t="n">
         <v>700</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
         <v>700</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
         <v>700</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO30" t="n">
         <v>700</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX30" t="n">
         <v>7</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE30" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE30" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH30" t="n">
         <v>3.35</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK30" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8149,16 +8149,16 @@
         <v>7.4</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BP30" t="n">
         <v>12</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR30" t="n">
         <v>36</v>
@@ -8170,7 +8170,7 @@
         <v>11.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -8223,31 +8223,31 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="G31" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
         <v>4.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>1.35</v>
@@ -8256,10 +8256,10 @@
         <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
@@ -8271,13 +8271,13 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="X31" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y31" t="n">
         <v>24</v>
@@ -8289,7 +8289,7 @@
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AC31" t="n">
         <v>9.4</v>
@@ -8316,34 +8316,34 @@
         <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
         <v>5.7</v>
@@ -8352,37 +8352,37 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>10.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BB31" t="n">
         <v>11.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="n">
         <v>7.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>2.04</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
         <v>3.95</v>
       </c>
       <c r="J32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.31</v>
@@ -8510,19 +8510,19 @@
         <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R32" t="n">
         <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
         <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V32" t="n">
         <v>1.34</v>
@@ -8531,34 +8531,34 @@
         <v>1.96</v>
       </c>
       <c r="X32" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z32" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA32" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>12</v>
       </c>
       <c r="AC32" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AE32" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF32" t="n">
         <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
         <v>17.5</v>
@@ -8570,7 +8570,7 @@
         <v>25</v>
       </c>
       <c r="AK32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL32" t="n">
         <v>34</v>
@@ -8585,34 +8585,34 @@
         <v>36</v>
       </c>
       <c r="AP32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AT32" t="n">
         <v>10.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV32" t="n">
         <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
         <v>14</v>
@@ -8621,22 +8621,22 @@
         <v>38</v>
       </c>
       <c r="BB32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC32" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE32" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH32" t="n">
         <v>4.2</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>4.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
@@ -8788,7 +8788,7 @@
         <v>36</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z33" t="n">
         <v>19</v>
@@ -8803,10 +8803,10 @@
         <v>12.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="n">
         <v>36</v>
@@ -8833,22 +8833,22 @@
         <v>60</v>
       </c>
       <c r="AN33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AP33" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR33" t="n">
         <v>13</v>
       </c>
       <c r="AS33" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AT33" t="n">
         <v>18</v>
@@ -8857,10 +8857,10 @@
         <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AX33" t="n">
         <v>16</v>
@@ -8875,7 +8875,7 @@
         <v>17</v>
       </c>
       <c r="BB33" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BC33" t="n">
         <v>24</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -8985,37 +8985,37 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O34" t="n">
         <v>1.57</v>
       </c>
       <c r="P34" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q34" t="n">
         <v>2.72</v>
@@ -9033,10 +9033,10 @@
         <v>1.76</v>
       </c>
       <c r="V34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W34" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X34" t="n">
         <v>8.800000000000001</v>
@@ -9054,7 +9054,7 @@
         <v>7.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD34" t="n">
         <v>16</v>
@@ -9093,10 +9093,10 @@
         <v>210</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR34" t="n">
         <v>18.5</v>
@@ -9108,7 +9108,7 @@
         <v>6.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV34" t="n">
         <v>13</v>
@@ -9126,7 +9126,7 @@
         <v>19.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB34" t="n">
         <v>34</v>
@@ -9138,13 +9138,13 @@
         <v>28</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF34" t="n">
         <v>38</v>
       </c>
       <c r="BG34" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BH34" t="n">
         <v>2.7</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -9245,16 +9245,16 @@
         <v>2.54</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L35" t="n">
         <v>1.6</v>
@@ -9287,7 +9287,7 @@
         <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
         <v>1.65</v>
@@ -9341,13 +9341,13 @@
         <v>500</v>
       </c>
       <c r="AN35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AQ35" t="n">
         <v>4.1</v>
@@ -9356,13 +9356,13 @@
         <v>5.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV35" t="n">
         <v>5</v>
@@ -9380,7 +9380,7 @@
         <v>5.3</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB35" t="n">
         <v>5.6</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G36" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
         <v>5</v>
@@ -9508,7 +9508,7 @@
         <v>2.98</v>
       </c>
       <c r="K36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.49</v>
@@ -9526,7 +9526,7 @@
         <v>1.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R36" t="n">
         <v>1.24</v>
@@ -9541,10 +9541,10 @@
         <v>1.82</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X36" t="n">
         <v>21</v>
@@ -9595,10 +9595,10 @@
         <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO36" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP36" t="n">
         <v>8.6</v>
@@ -9616,7 +9616,7 @@
         <v>6.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV36" t="n">
         <v>6</v>
@@ -9631,16 +9631,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="BA36" t="n">
         <v>2.88</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BC36" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="BD36" t="n">
         <v>2.78</v>
@@ -9649,7 +9649,7 @@
         <v>2.88</v>
       </c>
       <c r="BF36" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BG36" t="n">
         <v>2.88</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -9756,13 +9756,13 @@
         <v>1.65</v>
       </c>
       <c r="I37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J37" t="n">
         <v>3.55</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.44</v>
@@ -9777,7 +9777,7 @@
         <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q37" t="n">
         <v>2.14</v>
@@ -9792,7 +9792,7 @@
         <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V37" t="n">
         <v>2.34</v>
@@ -9864,7 +9864,7 @@
         <v>7.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AT37" t="n">
         <v>5.7</v>
@@ -9876,7 +9876,7 @@
         <v>8.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="AX37" t="n">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>21</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
         <v>7</v>
@@ -9918,7 +9918,7 @@
         <v>12.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -10001,25 +10001,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G38" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H38" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I38" t="n">
         <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="M38" t="n">
         <v>1.12</v>
@@ -10034,25 +10034,25 @@
         <v>1.53</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R38" t="n">
         <v>1.19</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T38" t="n">
         <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V38" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W38" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X38" t="n">
         <v>970</v>
@@ -10067,7 +10067,7 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AC38" t="n">
         <v>16.5</v>
@@ -10091,7 +10091,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="AK38" t="n">
         <v>500</v>
@@ -10112,10 +10112,10 @@
         <v>4.9</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS38" t="n">
         <v>4.2</v>
@@ -10127,7 +10127,7 @@
         <v>7.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW38" t="n">
         <v>4.2</v>
@@ -10139,22 +10139,22 @@
         <v>8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BA38" t="n">
         <v>4.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF38" t="n">
         <v>8</v>
@@ -10163,68 +10163,68 @@
         <v>4.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G39" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I39" t="n">
         <v>6.2</v>
@@ -10288,7 +10288,7 @@
         <v>1.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
@@ -10297,40 +10297,40 @@
         <v>5.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U39" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V39" t="n">
         <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y39" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z39" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA39" t="n">
         <v>900</v>
       </c>
       <c r="AB39" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE39" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF39" t="n">
         <v>10.5</v>
@@ -10339,13 +10339,13 @@
         <v>12</v>
       </c>
       <c r="AH39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI39" t="n">
         <v>170</v>
       </c>
       <c r="AJ39" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK39" t="n">
         <v>29</v>
@@ -10363,25 +10363,25 @@
         <v>700</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR39" t="n">
         <v>28</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="AW39" t="n">
         <v>8.199999999999999</v>
@@ -10390,7 +10390,7 @@
         <v>8</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
         <v>18</v>
@@ -10399,13 +10399,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC39" t="n">
         <v>17.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE39" t="n">
         <v>8.4</v>
@@ -10423,7 +10423,7 @@
         <v>2.26</v>
       </c>
       <c r="BJ39" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK39" t="n">
         <v>8</v>
@@ -10432,16 +10432,16 @@
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP39" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BQ39" t="n">
         <v>9.6</v>
@@ -10450,25 +10450,25 @@
         <v>44</v>
       </c>
       <c r="BS39" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW39" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -10763,25 +10763,25 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I41" t="n">
         <v>12</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M41" t="n">
         <v>1.02</v>
@@ -10796,16 +10796,16 @@
         <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R41" t="n">
         <v>1.69</v>
       </c>
       <c r="S41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T41" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U41" t="n">
         <v>2</v>
@@ -10814,7 +10814,7 @@
         <v>1.09</v>
       </c>
       <c r="W41" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="X41" t="n">
         <v>950</v>
@@ -10829,7 +10829,7 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
         <v>42</v>
@@ -10841,7 +10841,7 @@
         <v>170</v>
       </c>
       <c r="AF41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG41" t="n">
         <v>13</v>
@@ -10862,25 +10862,25 @@
         <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN41" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO41" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP41" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT41" t="n">
         <v>9.800000000000001</v>
@@ -10889,10 +10889,10 @@
         <v>11</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX41" t="n">
         <v>8.6</v>
@@ -10904,7 +10904,7 @@
         <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB41" t="n">
         <v>9</v>
@@ -10913,70 +10913,70 @@
         <v>10.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF41" t="n">
         <v>3.35</v>
       </c>
       <c r="BG41" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -11020,13 +11020,13 @@
         <v>1.42</v>
       </c>
       <c r="G42" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H42" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>5.3</v>
@@ -11035,7 +11035,7 @@
         <v>6.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M42" t="n">
         <v>1.02</v>
@@ -11125,7 +11125,7 @@
         <v>90</v>
       </c>
       <c r="AP42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ42" t="n">
         <v>23</v>
@@ -11155,10 +11155,10 @@
         <v>6.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB42" t="n">
         <v>8.4</v>
@@ -11167,80 +11167,80 @@
         <v>7.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BE42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF42" t="n">
         <v>4</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -11295,16 +11295,16 @@
         <v>1.04</v>
       </c>
       <c r="N43" t="n">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="O43" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R43" t="n">
         <v>1.46</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G44" t="n">
         <v>3.15</v>
@@ -11534,7 +11534,7 @@
         <v>2.36</v>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J44" t="n">
         <v>3.6</v>
@@ -11543,7 +11543,7 @@
         <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M44" t="n">
         <v>1.05</v>
@@ -11552,10 +11552,10 @@
         <v>4.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P44" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q44" t="n">
         <v>1.7</v>
@@ -11573,10 +11573,10 @@
         <v>2.42</v>
       </c>
       <c r="V44" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W44" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X44" t="n">
         <v>23</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -11782,19 +11782,19 @@
         <v>2.72</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H45" t="n">
         <v>2.64</v>
       </c>
       <c r="I45" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.3</v>
@@ -11830,7 +11830,7 @@
         <v>1.54</v>
       </c>
       <c r="W45" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X45" t="n">
         <v>18</v>
@@ -11890,49 +11890,49 @@
         <v>14</v>
       </c>
       <c r="AQ45" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR45" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS45" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT45" t="n">
         <v>11</v>
       </c>
       <c r="AU45" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX45" t="n">
         <v>14.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ45" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA45" t="n">
         <v>30</v>
       </c>
       <c r="BB45" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BC45" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD45" t="n">
         <v>27</v>
       </c>
       <c r="BE45" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BF45" t="n">
         <v>16.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -12293,19 +12293,19 @@
         <v>1.35</v>
       </c>
       <c r="H47" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I47" t="n">
         <v>11.5</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K47" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L47" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M47" t="n">
         <v>1.02</v>
@@ -12338,7 +12338,7 @@
         <v>1.09</v>
       </c>
       <c r="W47" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X47" t="n">
         <v>110</v>
@@ -12356,7 +12356,7 @@
         <v>17</v>
       </c>
       <c r="AC47" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD47" t="n">
         <v>46</v>
@@ -12398,13 +12398,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT47" t="n">
         <v>10.5</v>
@@ -12416,7 +12416,7 @@
         <v>18</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX47" t="n">
         <v>7.8</v>
@@ -12428,7 +12428,7 @@
         <v>19</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB47" t="n">
         <v>9.800000000000001</v>
@@ -12440,31 +12440,31 @@
         <v>21</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF47" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BG47" t="n">
         <v>10.5</v>
       </c>
       <c r="BH47" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ47" t="n">
         <v>11.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN47" t="n">
         <v>4.5</v>
@@ -12473,7 +12473,7 @@
         <v>3.35</v>
       </c>
       <c r="BP47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ47" t="n">
         <v>5.5</v>
@@ -12488,29 +12488,29 @@
         <v>14</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CA47" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G48" t="n">
         <v>3.05</v>
@@ -12556,34 +12556,34 @@
         <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.44</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="O48" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P48" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R48" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S48" t="n">
         <v>4.5</v>
       </c>
       <c r="T48" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U48" t="n">
         <v>1.89</v>
@@ -12601,7 +12601,7 @@
         <v>12</v>
       </c>
       <c r="Z48" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA48" t="n">
         <v>900</v>
@@ -12622,7 +12622,7 @@
         <v>500</v>
       </c>
       <c r="AG48" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AH48" t="n">
         <v>950</v>
@@ -12655,70 +12655,70 @@
         <v>7.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AU48" t="n">
         <v>5.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AW48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX48" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX48" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AY48" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AZ48" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB48" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB48" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC48" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH48" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
@@ -12730,13 +12730,13 @@
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
@@ -12748,23 +12748,23 @@
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -12849,10 +12849,10 @@
         <v>1.94</v>
       </c>
       <c r="X49" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z49" t="n">
         <v>500</v>
@@ -12861,7 +12861,7 @@
         <v>900</v>
       </c>
       <c r="AB49" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AC49" t="n">
         <v>8.4</v>
@@ -12873,10 +12873,10 @@
         <v>700</v>
       </c>
       <c r="AF49" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG49" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AH49" t="n">
         <v>950</v>
@@ -12903,28 +12903,28 @@
         <v>700</v>
       </c>
       <c r="AP49" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ49" t="n">
         <v>10</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.68</v>
+        <v>7.2</v>
       </c>
       <c r="AX49" t="n">
         <v>7.6</v>
@@ -12933,92 +12933,92 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK49" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA49" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN49" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -13052,61 +13052,61 @@
         <v>1.87</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J50" t="n">
         <v>2.92</v>
       </c>
       <c r="K50" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N50" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="O50" t="n">
         <v>1.65</v>
       </c>
       <c r="P50" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="R50" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S50" t="n">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="T50" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U50" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V50" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W50" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X50" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z50" t="n">
         <v>500</v>
@@ -13115,10 +13115,10 @@
         <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC50" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD50" t="n">
         <v>950</v>
@@ -13127,10 +13127,10 @@
         <v>700</v>
       </c>
       <c r="AF50" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG50" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH50" t="n">
         <v>950</v>
@@ -13157,58 +13157,58 @@
         <v>700</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
         <v>3.05</v>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="M51" t="n">
         <v>1.16</v>
@@ -13357,7 +13357,7 @@
         <v>1.5</v>
       </c>
       <c r="X51" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Y51" t="n">
         <v>9.199999999999999</v>
@@ -13372,10 +13372,10 @@
         <v>7.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AE51" t="n">
         <v>500</v>
@@ -13384,13 +13384,13 @@
         <v>970</v>
       </c>
       <c r="AG51" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH51" t="n">
         <v>950</v>
       </c>
       <c r="AI51" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ51" t="n">
         <v>500</v>
@@ -13411,7 +13411,7 @@
         <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ51" t="n">
         <v>6.4</v>
@@ -13420,19 +13420,19 @@
         <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU51" t="n">
         <v>5.5</v>
       </c>
       <c r="AV51" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX51" t="n">
         <v>12.5</v>
@@ -13441,37 +13441,37 @@
         <v>11</v>
       </c>
       <c r="AZ51" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BH51" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ51" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK51" t="n">
         <v>1.04</v>
@@ -13483,10 +13483,10 @@
         <v>1.04</v>
       </c>
       <c r="BN51" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
@@ -13501,10 +13501,10 @@
         <v>1.04</v>
       </c>
       <c r="BT51" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G52" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H52" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J52" t="n">
         <v>4.5</v>
       </c>
       <c r="K52" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,16 +13581,16 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="O52" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P52" t="n">
         <v>3.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="R52" t="n">
         <v>2.04</v>
@@ -13599,124 +13599,124 @@
         <v>1.72</v>
       </c>
       <c r="T52" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="U52" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X52" t="n">
         <v>950</v>
       </c>
       <c r="Y52" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Z52" t="n">
         <v>500</v>
       </c>
       <c r="AA52" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB52" t="n">
         <v>950</v>
       </c>
       <c r="AC52" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD52" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AE52" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AF52" t="n">
         <v>500</v>
       </c>
       <c r="AG52" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AH52" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI52" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ52" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK52" t="n">
         <v>500</v>
       </c>
       <c r="AL52" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM52" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN52" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AO52" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -13811,52 +13811,52 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="H53" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="I53" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L53" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M53" t="n">
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O53" t="n">
         <v>1.1</v>
       </c>
-      <c r="O53" t="n">
-        <v>1.07</v>
-      </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="R53" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="S53" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="T53" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="U53" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V53" t="n">
         <v>1.01</v>
@@ -13865,166 +13865,166 @@
         <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y53" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Z53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB53" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AC53" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE53" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF53" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AG53" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AH53" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ53" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK53" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AL53" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AM53" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN53" t="n">
-        <v>500</v>
+        <v>5.2</v>
       </c>
       <c r="AO53" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH53" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BJ53" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BN53" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO53" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP53" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT53" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU53" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV53" t="n">
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
         <v>4.2</v>
       </c>
       <c r="K54" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14113,7 +14113,7 @@
         <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W54" t="n">
         <v>1.51</v>
@@ -14134,7 +14134,7 @@
         <v>950</v>
       </c>
       <c r="AC54" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD54" t="n">
         <v>950</v>
@@ -14173,58 +14173,58 @@
         <v>500</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -14325,7 +14325,7 @@
         <v>1.95</v>
       </c>
       <c r="H55" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I55" t="n">
         <v>4.3</v>
@@ -14388,10 +14388,10 @@
         <v>950</v>
       </c>
       <c r="AC55" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AD55" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE55" t="n">
         <v>500</v>
@@ -14403,7 +14403,7 @@
         <v>14.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI55" t="n">
         <v>500</v>
@@ -14418,13 +14418,13 @@
         <v>500</v>
       </c>
       <c r="AM55" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN55" t="n">
         <v>7.4</v>
       </c>
       <c r="AO55" t="n">
-        <v>970</v>
+        <v>240</v>
       </c>
       <c r="AP55" t="n">
         <v>6.6</v>
@@ -14460,7 +14460,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB55" t="n">
         <v>4.3</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <v>4.9</v>
       </c>
       <c r="J56" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K56" t="n">
         <v>3.5</v>
@@ -14597,7 +14597,7 @@
         <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O56" t="n">
         <v>1.49</v>
@@ -14630,7 +14630,7 @@
         <v>11</v>
       </c>
       <c r="Y56" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
         <v>34</v>
@@ -14672,7 +14672,7 @@
         <v>65</v>
       </c>
       <c r="AM56" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN56" t="n">
         <v>28</v>
@@ -14690,7 +14690,7 @@
         <v>21</v>
       </c>
       <c r="AS56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT56" t="n">
         <v>5.6</v>
@@ -14702,7 +14702,7 @@
         <v>14.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX56" t="n">
         <v>9</v>
@@ -14711,10 +14711,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ56" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB56" t="n">
         <v>20</v>
@@ -14726,13 +14726,13 @@
         <v>36</v>
       </c>
       <c r="BE56" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF56" t="n">
         <v>18</v>
       </c>
       <c r="BG56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH56" t="n">
         <v>2.9</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -14836,13 +14836,13 @@
         <v>3.25</v>
       </c>
       <c r="I57" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>3.35</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L57" t="n">
         <v>1.4</v>
@@ -14851,7 +14851,7 @@
         <v>1.09</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
         <v>1.42</v>
@@ -14860,19 +14860,19 @@
         <v>1.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R57" t="n">
         <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T57" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U57" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V57" t="n">
         <v>1.39</v>
@@ -14893,7 +14893,7 @@
         <v>900</v>
       </c>
       <c r="AB57" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC57" t="n">
         <v>7.8</v>
@@ -14941,10 +14941,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR57" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT57" t="n">
         <v>6.4</v>
@@ -14956,7 +14956,7 @@
         <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX57" t="n">
         <v>10.5</v>
@@ -14968,25 +14968,25 @@
         <v>17.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB57" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC57" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF57" t="n">
         <v>20</v>
       </c>
       <c r="BG57" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH57" t="n">
         <v>3.05</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G58" t="n">
         <v>2.04</v>
@@ -15093,7 +15093,7 @@
         <v>5.7</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
         <v>3.35</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15748,7 @@
         <v>4.1</v>
       </c>
       <c r="BG60" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BH60" t="n">
         <v>5.6</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
         <v>2.42</v>
       </c>
       <c r="V61" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="W61" t="n">
         <v>1.15</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
         <v>2.6</v>
       </c>
       <c r="R62" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S62" t="n">
         <v>5.4</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -16617,19 +16617,19 @@
         <v>3.75</v>
       </c>
       <c r="J64" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K64" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L64" t="n">
         <v>1.44</v>
       </c>
       <c r="M64" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O64" t="n">
         <v>1.42</v>
@@ -16638,19 +16638,19 @@
         <v>1.58</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R64" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S64" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U64" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V64" t="n">
         <v>1.36</v>
@@ -16716,13 +16716,13 @@
         <v>3.65</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR64" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AT64" t="n">
         <v>3.4</v>
@@ -16734,7 +16734,7 @@
         <v>4</v>
       </c>
       <c r="AW64" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AX64" t="n">
         <v>4</v>
@@ -16749,28 +16749,28 @@
         <v>3.95</v>
       </c>
       <c r="BB64" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BC64" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG64" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH64" t="n">
         <v>4.7</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
@@ -16782,7 +16782,7 @@
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BN64" t="n">
         <v>1000</v>
@@ -16794,13 +16794,13 @@
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
@@ -16812,7 +16812,7 @@
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
@@ -16824,11 +16824,11 @@
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
         <v>2.7</v>
       </c>
       <c r="H65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I65" t="n">
         <v>3.75</v>
@@ -16886,13 +16886,13 @@
         <v>3.05</v>
       </c>
       <c r="O65" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P65" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R65" t="n">
         <v>1.25</v>
@@ -16904,7 +16904,7 @@
         <v>1.84</v>
       </c>
       <c r="U65" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V65" t="n">
         <v>1.36</v>
@@ -16931,7 +16931,7 @@
         <v>8</v>
       </c>
       <c r="AD65" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE65" t="n">
         <v>55</v>
@@ -16976,7 +16976,7 @@
         <v>16.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT65" t="n">
         <v>6.6</v>
@@ -16994,13 +16994,13 @@
         <v>12.5</v>
       </c>
       <c r="AY65" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ65" t="n">
         <v>14</v>
       </c>
       <c r="BA65" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB65" t="n">
         <v>5.6</v>
@@ -17009,7 +17009,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD65" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE65" t="n">
         <v>6.2</v>
@@ -17024,7 +17024,7 @@
         <v>3.2</v>
       </c>
       <c r="BI65" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ65" t="n">
         <v>11</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
         <v>1.71</v>
       </c>
       <c r="I66" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="J66" t="n">
         <v>4.6</v>
@@ -17152,7 +17152,7 @@
         <v>2</v>
       </c>
       <c r="S66" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T66" t="n">
         <v>1.41</v>
@@ -17260,7 +17260,7 @@
         <v>10</v>
       </c>
       <c r="BC66" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD66" t="n">
         <v>22</v>
@@ -17296,7 +17296,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO66" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BP66" t="n">
         <v>38</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
         <v>2.96</v>
       </c>
       <c r="K67" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L67" t="n">
         <v>1.59</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -17636,7 +17636,7 @@
         <v>3.15</v>
       </c>
       <c r="K68" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L68" t="n">
         <v>1.48</v>
@@ -17660,7 +17660,7 @@
         <v>1.2</v>
       </c>
       <c r="S68" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T68" t="n">
         <v>2.1</v>
@@ -17831,7 +17831,7 @@
         <v>9</v>
       </c>
       <c r="BX68" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY68" t="n">
         <v>9.800000000000001</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -17875,13 +17875,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G69" t="n">
         <v>2.3</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I69" t="n">
         <v>4.9</v>
@@ -17890,7 +17890,7 @@
         <v>2.88</v>
       </c>
       <c r="K69" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -17902,19 +17902,19 @@
         <v>2.4</v>
       </c>
       <c r="O69" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P69" t="n">
         <v>1.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R69" t="n">
         <v>1.17</v>
       </c>
       <c r="S69" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T69" t="n">
         <v>1.11</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,768 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Operario PR</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>80</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:23:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Barra FC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Amazonas FC</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>570</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>790</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:23:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ferroviaria</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Inter Limeira</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>430</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>410</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>800</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>800</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>6</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
